--- a/R/data/quiz_250324.xlsx
+++ b/R/data/quiz_250324.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="325">
   <si>
     <t>타임스탬프</t>
   </si>
@@ -605,6 +605,387 @@
   </si>
   <si>
     <t>정민교</t>
+  </si>
+  <si>
+    <t>minbh5642@gmail.com</t>
+  </si>
+  <si>
+    <t>인문학부</t>
+  </si>
+  <si>
+    <t>민병현</t>
+  </si>
+  <si>
+    <t>lgw200308@gmail.com</t>
+  </si>
+  <si>
+    <t>소프트웨어융합</t>
+  </si>
+  <si>
+    <t>이강우</t>
+  </si>
+  <si>
+    <t>leedahoon12@naver.com</t>
+  </si>
+  <si>
+    <t>이다훈</t>
+  </si>
+  <si>
+    <t>songchae43@gmail.com</t>
+  </si>
+  <si>
+    <t>송채연</t>
+  </si>
+  <si>
+    <t>hyunakim2005@gmail.com</t>
+  </si>
+  <si>
+    <t>김현아</t>
+  </si>
+  <si>
+    <t>huhjunwoo0@gmail.com</t>
+  </si>
+  <si>
+    <t>디지털미디어콘텐츠학과</t>
+  </si>
+  <si>
+    <t>허준우</t>
+  </si>
+  <si>
+    <t>kimdw9510@gmail.com</t>
+  </si>
+  <si>
+    <t>경제학과</t>
+  </si>
+  <si>
+    <t>김동우</t>
+  </si>
+  <si>
+    <t>seakim0515@naver.com</t>
+  </si>
+  <si>
+    <t>김세아</t>
+  </si>
+  <si>
+    <t>sarahmood@naver.com</t>
+  </si>
+  <si>
+    <t>복은비</t>
+  </si>
+  <si>
+    <t>20235110@hallym.ac.kr</t>
+  </si>
+  <si>
+    <t>소프트웨어학부</t>
+  </si>
+  <si>
+    <t>고유빈</t>
+  </si>
+  <si>
+    <t>bshtt2927@gmail.com</t>
+  </si>
+  <si>
+    <t>변세현</t>
+  </si>
+  <si>
+    <t>kimgyobum0705@gmail.com</t>
+  </si>
+  <si>
+    <t>김교범</t>
+  </si>
+  <si>
+    <t>hoperoy1213@gmail.com</t>
+  </si>
+  <si>
+    <t>AI로봇융합전공</t>
+  </si>
+  <si>
+    <t>최진호</t>
+  </si>
+  <si>
+    <t>jyk3642@naver.com</t>
+  </si>
+  <si>
+    <t>김정연</t>
+  </si>
+  <si>
+    <t>yj030207@naver.com</t>
+  </si>
+  <si>
+    <t>김유진</t>
+  </si>
+  <si>
+    <t>keh_0501@naver.com</t>
+  </si>
+  <si>
+    <t>김은화</t>
+  </si>
+  <si>
+    <t>heey7754@naver.com</t>
+  </si>
+  <si>
+    <t>이희연</t>
+  </si>
+  <si>
+    <t>ous4297@naver.com</t>
+  </si>
+  <si>
+    <t>융합관광경영</t>
+  </si>
+  <si>
+    <t>오윤서</t>
+  </si>
+  <si>
+    <t>manjo1234@naver.com</t>
+  </si>
+  <si>
+    <t>김민주</t>
+  </si>
+  <si>
+    <t>deoduck877@naver.com</t>
+  </si>
+  <si>
+    <t>김동규</t>
+  </si>
+  <si>
+    <t>kseoj123@naver.com</t>
+  </si>
+  <si>
+    <t>김서진</t>
+  </si>
+  <si>
+    <t>capjjjmj@naver.com</t>
+  </si>
+  <si>
+    <t>국어국문학과</t>
+  </si>
+  <si>
+    <t>전민정</t>
+  </si>
+  <si>
+    <t>wnsduq285@gmail.com</t>
+  </si>
+  <si>
+    <t>박준엽</t>
+  </si>
+  <si>
+    <t>yoonji3795@naver.com</t>
+  </si>
+  <si>
+    <t>미래융합스쿨 융합관광경영전공</t>
+  </si>
+  <si>
+    <t>김윤지</t>
+  </si>
+  <si>
+    <t>hjykmj0916@gmail.com</t>
+  </si>
+  <si>
+    <t>사학과</t>
+  </si>
+  <si>
+    <t>김유경</t>
+  </si>
+  <si>
+    <t>hyehwi0807@naver.com</t>
+  </si>
+  <si>
+    <t>러시아학과</t>
+  </si>
+  <si>
+    <t>김혜빈</t>
+  </si>
+  <si>
+    <t>wodyd011324@gmail.com</t>
+  </si>
+  <si>
+    <t>김준형</t>
+  </si>
+  <si>
+    <t>seoyeonjang0418@naver.com</t>
+  </si>
+  <si>
+    <t>장서연</t>
+  </si>
+  <si>
+    <t>dongil00001@naver.com</t>
+  </si>
+  <si>
+    <t>김동일</t>
+  </si>
+  <si>
+    <t>dragon2003n@naver.com</t>
+  </si>
+  <si>
+    <t>이진우</t>
+  </si>
+  <si>
+    <t>326310@naver.com</t>
+  </si>
+  <si>
+    <t>힌승희</t>
+  </si>
+  <si>
+    <t>choije0115@naver.com</t>
+  </si>
+  <si>
+    <t>최정은</t>
+  </si>
+  <si>
+    <t>rmsdud9740@naver.com</t>
+  </si>
+  <si>
+    <t>경영</t>
+  </si>
+  <si>
+    <t>임근영</t>
+  </si>
+  <si>
+    <t>othernumber@naver.com</t>
+  </si>
+  <si>
+    <t>정서윤</t>
+  </si>
+  <si>
+    <t>lkj1526@naver.com</t>
+  </si>
+  <si>
+    <t>콘텐츠it전공</t>
+  </si>
+  <si>
+    <t>심건우</t>
+  </si>
+  <si>
+    <t>sy123312@naver.com</t>
+  </si>
+  <si>
+    <t>정선영</t>
+  </si>
+  <si>
+    <t>ngjh1026@gmail.com</t>
+  </si>
+  <si>
+    <t>남궁정현</t>
+  </si>
+  <si>
+    <t>yeri_3701@naver.com</t>
+  </si>
+  <si>
+    <t>김소현</t>
+  </si>
+  <si>
+    <t>cara3364@naver.com</t>
+  </si>
+  <si>
+    <t>최수연</t>
+  </si>
+  <si>
+    <t>yeeun051212@naver.com</t>
+  </si>
+  <si>
+    <t>진예은</t>
+  </si>
+  <si>
+    <t>ggt0826@naver.com</t>
+  </si>
+  <si>
+    <t>김경태</t>
+  </si>
+  <si>
+    <t>20216509@hallym.ac.kr</t>
+  </si>
+  <si>
+    <t>AI의료융합전공</t>
+  </si>
+  <si>
+    <t>김지섭</t>
+  </si>
+  <si>
+    <t>ko095013@gmail.com</t>
+  </si>
+  <si>
+    <t>고준영</t>
+  </si>
+  <si>
+    <t>3628kyl@naver.com</t>
+  </si>
+  <si>
+    <t>권혜수</t>
+  </si>
+  <si>
+    <t>swl0427@naver.com</t>
+  </si>
+  <si>
+    <t>이승우</t>
+  </si>
+  <si>
+    <t>donghun2477@naver.com</t>
+  </si>
+  <si>
+    <t>한동훈</t>
+  </si>
+  <si>
+    <t>kuen0508217@naver.com</t>
+  </si>
+  <si>
+    <t>권가영</t>
+  </si>
+  <si>
+    <t>shinhyeonho79@gmail.com</t>
+  </si>
+  <si>
+    <t>신현호</t>
+  </si>
+  <si>
+    <t>sihyun5170@naver.com</t>
+  </si>
+  <si>
+    <t>박시현</t>
+  </si>
+  <si>
+    <t>dahyeon057@naver.com</t>
+  </si>
+  <si>
+    <t>한다현</t>
+  </si>
+  <si>
+    <t>misobell520@naver.com</t>
+  </si>
+  <si>
+    <t>디지털미디어콘텐츠전공</t>
+  </si>
+  <si>
+    <t>이현희</t>
+  </si>
+  <si>
+    <t>renatta@naver.com</t>
+  </si>
+  <si>
+    <t>사회복지학부</t>
+  </si>
+  <si>
+    <t>이예원</t>
+  </si>
+  <si>
+    <t>maniddom@gmail.com</t>
+  </si>
+  <si>
+    <t>이민준</t>
+  </si>
+  <si>
+    <t>parkchaebin7890@gmail.com</t>
+  </si>
+  <si>
+    <t>디지털미디어콘텐츠 전공</t>
+  </si>
+  <si>
+    <t>maniaeom@gmail.com</t>
+  </si>
+  <si>
+    <t>청각학전공</t>
+  </si>
+  <si>
+    <t>엄지은</t>
   </si>
 </sst>
 </file>
@@ -768,10 +1149,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -779,13 +1160,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -932,7 +1313,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A1:N60" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A1:N115" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="14">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -3599,44 +3980,2299 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="23">
+      <c r="A60" s="15">
         <v>45741.55927824074</v>
       </c>
-      <c r="B60" s="24" t="s">
+      <c r="B60" s="16" t="s">
         <v>196</v>
       </c>
-      <c r="C60" s="24" t="s">
+      <c r="C60" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="D60" s="24">
+      <c r="D60" s="16">
         <v>2.0212638E7</v>
       </c>
-      <c r="E60" s="24" t="s">
+      <c r="E60" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="F60" s="24" t="s">
+      <c r="F60" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="G60" s="25">
+      <c r="G60" s="17">
         <v>0.9</v>
       </c>
-      <c r="H60" s="24" t="s">
+      <c r="H60" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="I60" s="24" t="s">
+      <c r="I60" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="J60" s="24" t="s">
+      <c r="J60" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="K60" s="24" t="s">
+      <c r="K60" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="L60" s="24" t="s">
+      <c r="L60" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="M60" s="24" t="s">
+      <c r="M60" s="16" t="s">
         <v>94</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="19">
+        <v>45741.64999895833</v>
+      </c>
+      <c r="B61" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="C61" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="D61" s="20">
+        <v>2.0251036E7</v>
+      </c>
+      <c r="E61" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="F61" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G61" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H61" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I61" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="J61" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K61" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L61" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N61" s="22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="15">
+        <v>45741.650555995366</v>
+      </c>
+      <c r="B62" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="C62" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="D62" s="16">
+        <v>2.0225208E7</v>
+      </c>
+      <c r="E62" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="F62" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G62" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H62" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I62" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="J62" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K62" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L62" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N62" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="19">
+        <v>45741.66819415509</v>
+      </c>
+      <c r="B63" s="20" t="s">
+        <v>204</v>
+      </c>
+      <c r="C63" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D63" s="20">
+        <v>2.0182936E7</v>
+      </c>
+      <c r="E63" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="F63" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G63" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="H63" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I63" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="J63" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K63" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="L63" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N63" s="22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="15">
+        <v>45741.6754481713</v>
+      </c>
+      <c r="B64" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="C64" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D64" s="16">
+        <v>2.0243519E7</v>
+      </c>
+      <c r="E64" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="F64" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="G64" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="H64" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I64" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="J64" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K64" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="L64" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M64" s="16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="19">
+        <v>45741.67945784722</v>
+      </c>
+      <c r="B65" s="20" t="s">
+        <v>208</v>
+      </c>
+      <c r="C65" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="D65" s="20">
+        <v>2.0243507E7</v>
+      </c>
+      <c r="E65" s="20" t="s">
+        <v>209</v>
+      </c>
+      <c r="F65" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G65" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="H65" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I65" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="J65" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K65" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="L65" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M65" s="20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="15">
+        <v>45741.69365984954</v>
+      </c>
+      <c r="B66" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="C66" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="D66" s="16">
+        <v>2.0246792E7</v>
+      </c>
+      <c r="E66" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="F66" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G66" s="17">
+        <v>0.7</v>
+      </c>
+      <c r="H66" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="I66" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="J66" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K66" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="L66" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N66" s="18" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="19">
+        <v>45741.72709100695</v>
+      </c>
+      <c r="B67" s="20" t="s">
+        <v>213</v>
+      </c>
+      <c r="C67" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="D67" s="20">
+        <v>2.0242807E7</v>
+      </c>
+      <c r="E67" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="F67" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G67" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="H67" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I67" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J67" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K67" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="L67" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N67" s="22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="15">
+        <v>45741.75274185185</v>
+      </c>
+      <c r="B68" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="C68" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="D68" s="16">
+        <v>2.023271E7</v>
+      </c>
+      <c r="E68" s="16" t="s">
+        <v>217</v>
+      </c>
+      <c r="F68" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="G68" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="H68" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I68" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="J68" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K68" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L68" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M68" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="19">
+        <v>45741.76996712963</v>
+      </c>
+      <c r="B69" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="C69" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="D69" s="20">
+        <v>2.0222823E7</v>
+      </c>
+      <c r="E69" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="F69" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G69" s="21">
+        <v>0.9</v>
+      </c>
+      <c r="H69" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="I69" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J69" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K69" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="L69" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N69" s="22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="15">
+        <v>45741.77338436343</v>
+      </c>
+      <c r="B70" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="C70" s="16" t="s">
+        <v>221</v>
+      </c>
+      <c r="D70" s="16">
+        <v>2.023511E7</v>
+      </c>
+      <c r="E70" s="16" t="s">
+        <v>222</v>
+      </c>
+      <c r="F70" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G70" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="H70" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I70" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J70" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K70" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L70" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N70" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="19">
+        <v>45741.781891307866</v>
+      </c>
+      <c r="B71" s="20" t="s">
+        <v>223</v>
+      </c>
+      <c r="C71" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D71" s="20">
+        <v>2.0211713E7</v>
+      </c>
+      <c r="E71" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="F71" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G71" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H71" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I71" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J71" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="K71" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="L71" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N71" s="22" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="15">
+        <v>45741.78382635416</v>
+      </c>
+      <c r="B72" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="C72" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D72" s="16">
+        <v>2.0241507E7</v>
+      </c>
+      <c r="E72" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="F72" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G72" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H72" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I72" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="J72" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K72" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L72" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M72" s="16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="19">
+        <v>45741.8266394213</v>
+      </c>
+      <c r="B73" s="20" t="s">
+        <v>227</v>
+      </c>
+      <c r="C73" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="D73" s="20">
+        <v>2.0246789E7</v>
+      </c>
+      <c r="E73" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="F73" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G73" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="H73" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I73" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="J73" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K73" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="L73" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M73" s="20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="15">
+        <v>45741.86321034722</v>
+      </c>
+      <c r="B74" s="16" t="s">
+        <v>230</v>
+      </c>
+      <c r="C74" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="D74" s="16">
+        <v>2.022708E7</v>
+      </c>
+      <c r="E74" s="16" t="s">
+        <v>231</v>
+      </c>
+      <c r="F74" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G74" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H74" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I74" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="J74" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K74" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L74" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M74" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="19">
+        <v>45741.86573181713</v>
+      </c>
+      <c r="B75" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="C75" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="D75" s="20">
+        <v>2.0233306E7</v>
+      </c>
+      <c r="E75" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="F75" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G75" s="21">
+        <v>0.7</v>
+      </c>
+      <c r="H75" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I75" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J75" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K75" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="L75" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M75" s="20" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="15">
+        <v>45741.886143634256</v>
+      </c>
+      <c r="B76" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="C76" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="D76" s="16">
+        <v>2.024221E7</v>
+      </c>
+      <c r="E76" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="F76" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G76" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H76" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="I76" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="J76" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K76" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="L76" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N76" s="18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="19">
+        <v>45741.89262633101</v>
+      </c>
+      <c r="B77" s="20" t="s">
+        <v>236</v>
+      </c>
+      <c r="C77" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="D77" s="20">
+        <v>2.0246275E7</v>
+      </c>
+      <c r="E77" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="F77" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="G77" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="H77" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="I77" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="J77" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K77" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="L77" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N77" s="22" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="15">
+        <v>45741.89512527778</v>
+      </c>
+      <c r="B78" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="C78" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="D78" s="16">
+        <v>2.0246632E7</v>
+      </c>
+      <c r="E78" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="F78" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G78" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H78" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I78" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J78" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K78" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L78" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M78" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="19">
+        <v>45741.90215440972</v>
+      </c>
+      <c r="B79" s="20" t="s">
+        <v>241</v>
+      </c>
+      <c r="C79" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="D79" s="20">
+        <v>2.0246912E7</v>
+      </c>
+      <c r="E79" s="20" t="s">
+        <v>242</v>
+      </c>
+      <c r="F79" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G79" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H79" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I79" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J79" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K79" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L79" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M79" s="20" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="15">
+        <v>45741.90520149306</v>
+      </c>
+      <c r="B80" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="C80" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="D80" s="16">
+        <v>2.0195122E7</v>
+      </c>
+      <c r="E80" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="F80" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G80" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H80" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I80" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J80" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K80" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L80" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M80" s="16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="19">
+        <v>45741.97831276621</v>
+      </c>
+      <c r="B81" s="20" t="s">
+        <v>245</v>
+      </c>
+      <c r="C81" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="D81" s="20">
+        <v>2.0243906E7</v>
+      </c>
+      <c r="E81" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="F81" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G81" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H81" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I81" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J81" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K81" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L81" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N81" s="22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="15">
+        <v>45742.00602994213</v>
+      </c>
+      <c r="B82" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="C82" s="16" t="s">
+        <v>248</v>
+      </c>
+      <c r="D82" s="16">
+        <v>2.0241085E7</v>
+      </c>
+      <c r="E82" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="F82" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G82" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="H82" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I82" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="J82" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="K82" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L82" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N82" s="18" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="19">
+        <v>45742.019170879634</v>
+      </c>
+      <c r="B83" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="C83" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="D83" s="20">
+        <v>2.0227096E7</v>
+      </c>
+      <c r="E83" s="20" t="s">
+        <v>251</v>
+      </c>
+      <c r="F83" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G83" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="H83" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="I83" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J83" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K83" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="L83" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N83" s="22" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="15">
+        <v>45742.02318373843</v>
+      </c>
+      <c r="B84" s="16" t="s">
+        <v>252</v>
+      </c>
+      <c r="C84" s="16" t="s">
+        <v>253</v>
+      </c>
+      <c r="D84" s="16">
+        <v>2.0227125E7</v>
+      </c>
+      <c r="E84" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="F84" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G84" s="17">
+        <v>0.9</v>
+      </c>
+      <c r="H84" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="I84" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="J84" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K84" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L84" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N84" s="18" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="19">
+        <v>45742.03328635417</v>
+      </c>
+      <c r="B85" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="C85" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="D85" s="20">
+        <v>2.0241018E7</v>
+      </c>
+      <c r="E85" s="20" t="s">
+        <v>257</v>
+      </c>
+      <c r="F85" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G85" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H85" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I85" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="J85" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K85" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L85" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M85" s="20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="15">
+        <v>45742.03331396991</v>
+      </c>
+      <c r="B86" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="C86" s="16" t="s">
+        <v>259</v>
+      </c>
+      <c r="D86" s="16">
+        <v>2.0241711E7</v>
+      </c>
+      <c r="E86" s="16" t="s">
+        <v>260</v>
+      </c>
+      <c r="F86" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G86" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H86" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I86" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J86" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K86" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L86" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N86" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="19">
+        <v>45742.095714675925</v>
+      </c>
+      <c r="B87" s="20" t="s">
+        <v>261</v>
+      </c>
+      <c r="C87" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="D87" s="20">
+        <v>2.0215136E7</v>
+      </c>
+      <c r="E87" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="F87" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G87" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H87" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I87" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J87" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K87" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L87" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M87" s="20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="15">
+        <v>45742.38539322917</v>
+      </c>
+      <c r="B88" s="16" t="s">
+        <v>263</v>
+      </c>
+      <c r="C88" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="D88" s="16">
+        <v>2.0241232E7</v>
+      </c>
+      <c r="E88" s="16" t="s">
+        <v>264</v>
+      </c>
+      <c r="F88" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G88" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H88" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I88" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J88" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K88" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L88" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M88" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="19">
+        <v>45742.4247792824</v>
+      </c>
+      <c r="B89" s="20" t="s">
+        <v>265</v>
+      </c>
+      <c r="C89" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="D89" s="20">
+        <v>2.0232408E7</v>
+      </c>
+      <c r="E89" s="20" t="s">
+        <v>266</v>
+      </c>
+      <c r="F89" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G89" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H89" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I89" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J89" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K89" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L89" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M89" s="20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="15">
+        <v>45742.44222266204</v>
+      </c>
+      <c r="B90" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="C90" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="D90" s="16">
+        <v>2.0236281E7</v>
+      </c>
+      <c r="E90" s="16" t="s">
+        <v>268</v>
+      </c>
+      <c r="F90" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G90" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H90" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I90" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J90" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K90" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L90" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N90" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="19">
+        <v>45742.453773113426</v>
+      </c>
+      <c r="B91" s="20" t="s">
+        <v>269</v>
+      </c>
+      <c r="C91" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="D91" s="20">
+        <v>2.0221541E7</v>
+      </c>
+      <c r="E91" s="20" t="s">
+        <v>270</v>
+      </c>
+      <c r="F91" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G91" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="H91" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="I91" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="J91" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K91" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="L91" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M91" s="20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="15">
+        <v>45742.46296734954</v>
+      </c>
+      <c r="B92" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="C92" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D92" s="16">
+        <v>2.0233543E7</v>
+      </c>
+      <c r="E92" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="F92" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G92" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H92" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I92" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J92" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K92" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L92" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M92" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="19">
+        <v>45742.469896678245</v>
+      </c>
+      <c r="B93" s="20" t="s">
+        <v>273</v>
+      </c>
+      <c r="C93" s="20" t="s">
+        <v>274</v>
+      </c>
+      <c r="D93" s="20">
+        <v>2.0243019E7</v>
+      </c>
+      <c r="E93" s="20" t="s">
+        <v>275</v>
+      </c>
+      <c r="F93" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G93" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H93" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I93" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J93" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K93" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L93" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M93" s="20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="15">
+        <v>45742.49342427083</v>
+      </c>
+      <c r="B94" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="C94" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D94" s="16">
+        <v>2.0233033E7</v>
+      </c>
+      <c r="E94" s="16" t="s">
+        <v>277</v>
+      </c>
+      <c r="F94" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G94" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H94" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I94" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J94" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K94" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L94" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N94" s="18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="19">
+        <v>45742.501028680555</v>
+      </c>
+      <c r="B95" s="20" t="s">
+        <v>278</v>
+      </c>
+      <c r="C95" s="20" t="s">
+        <v>279</v>
+      </c>
+      <c r="D95" s="20">
+        <v>2.0215181E7</v>
+      </c>
+      <c r="E95" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="F95" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G95" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="H95" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I95" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J95" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K95" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L95" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N95" s="22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="15">
+        <v>45742.50670121528</v>
+      </c>
+      <c r="B96" s="16" t="s">
+        <v>281</v>
+      </c>
+      <c r="C96" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="D96" s="16">
+        <v>2.0223428E7</v>
+      </c>
+      <c r="E96" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="F96" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="G96" s="17">
+        <v>0.9</v>
+      </c>
+      <c r="H96" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I96" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J96" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K96" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="L96" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N96" s="18" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="19">
+        <v>45742.52714611111</v>
+      </c>
+      <c r="B97" s="20" t="s">
+        <v>283</v>
+      </c>
+      <c r="C97" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="D97" s="20">
+        <v>2.0232813E7</v>
+      </c>
+      <c r="E97" s="20" t="s">
+        <v>284</v>
+      </c>
+      <c r="F97" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G97" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H97" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I97" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="J97" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K97" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="L97" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M97" s="20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="15">
+        <v>45742.53234805555</v>
+      </c>
+      <c r="B98" s="16" t="s">
+        <v>285</v>
+      </c>
+      <c r="C98" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="D98" s="16">
+        <v>2.0232109E7</v>
+      </c>
+      <c r="E98" s="16" t="s">
+        <v>286</v>
+      </c>
+      <c r="F98" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G98" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H98" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I98" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="J98" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K98" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L98" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N98" s="18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="19">
+        <v>45742.543009560184</v>
+      </c>
+      <c r="B99" s="20" t="s">
+        <v>287</v>
+      </c>
+      <c r="C99" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="D99" s="20">
+        <v>2.0246295E7</v>
+      </c>
+      <c r="E99" s="20" t="s">
+        <v>288</v>
+      </c>
+      <c r="F99" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="G99" s="21">
+        <v>0.7</v>
+      </c>
+      <c r="H99" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="I99" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J99" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K99" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L99" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M99" s="20" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="15">
+        <v>45742.54691822917</v>
+      </c>
+      <c r="B100" s="16" t="s">
+        <v>289</v>
+      </c>
+      <c r="C100" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="D100" s="16">
+        <v>2.0243845E7</v>
+      </c>
+      <c r="E100" s="16" t="s">
+        <v>290</v>
+      </c>
+      <c r="F100" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G100" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H100" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I100" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J100" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K100" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L100" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N100" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="19">
+        <v>45742.61840569445</v>
+      </c>
+      <c r="B101" s="20" t="s">
+        <v>291</v>
+      </c>
+      <c r="C101" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="D101" s="20">
+        <v>2.0212703E7</v>
+      </c>
+      <c r="E101" s="20" t="s">
+        <v>292</v>
+      </c>
+      <c r="F101" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G101" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H101" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I101" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J101" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K101" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L101" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M101" s="20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="15">
+        <v>45742.64958704861</v>
+      </c>
+      <c r="B102" s="16" t="s">
+        <v>293</v>
+      </c>
+      <c r="C102" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="D102" s="16">
+        <v>2.0216509E7</v>
+      </c>
+      <c r="E102" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="F102" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G102" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H102" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I102" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="J102" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K102" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L102" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N102" s="18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="19">
+        <v>45742.69009319444</v>
+      </c>
+      <c r="B103" s="20" t="s">
+        <v>296</v>
+      </c>
+      <c r="C103" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="D103" s="20">
+        <v>2.0212403E7</v>
+      </c>
+      <c r="E103" s="20" t="s">
+        <v>297</v>
+      </c>
+      <c r="F103" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G103" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="H103" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="I103" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="J103" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K103" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="L103" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M103" s="20" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="15">
+        <v>45742.69954136574</v>
+      </c>
+      <c r="B104" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="C104" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="D104" s="16">
+        <v>2.0242605E7</v>
+      </c>
+      <c r="E104" s="16" t="s">
+        <v>299</v>
+      </c>
+      <c r="F104" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G104" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H104" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I104" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J104" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K104" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L104" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N104" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="19">
+        <v>45742.7121343287</v>
+      </c>
+      <c r="B105" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="C105" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D105" s="20">
+        <v>2.0223002E7</v>
+      </c>
+      <c r="E105" s="20" t="s">
+        <v>301</v>
+      </c>
+      <c r="F105" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G105" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H105" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I105" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="J105" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K105" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L105" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M105" s="20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="15">
+        <v>45742.71335637731</v>
+      </c>
+      <c r="B106" s="16" t="s">
+        <v>302</v>
+      </c>
+      <c r="C106" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="D106" s="16">
+        <v>2.0222761E7</v>
+      </c>
+      <c r="E106" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="F106" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G106" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H106" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="I106" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J106" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K106" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L106" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M106" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="19">
+        <v>45742.71742652778</v>
+      </c>
+      <c r="B107" s="20" t="s">
+        <v>304</v>
+      </c>
+      <c r="C107" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D107" s="20">
+        <v>2.0242909E7</v>
+      </c>
+      <c r="E107" s="20" t="s">
+        <v>305</v>
+      </c>
+      <c r="F107" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G107" s="21">
+        <v>0.9</v>
+      </c>
+      <c r="H107" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="I107" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="J107" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K107" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="L107" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N107" s="22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="15">
+        <v>45742.7291830787</v>
+      </c>
+      <c r="B108" s="16" t="s">
+        <v>306</v>
+      </c>
+      <c r="C108" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="D108" s="16">
+        <v>2.0243326E7</v>
+      </c>
+      <c r="E108" s="16" t="s">
+        <v>307</v>
+      </c>
+      <c r="F108" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G108" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H108" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I108" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J108" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K108" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L108" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N108" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="19">
+        <v>45742.73033701389</v>
+      </c>
+      <c r="B109" s="20" t="s">
+        <v>308</v>
+      </c>
+      <c r="C109" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="D109" s="20">
+        <v>2.0212214E7</v>
+      </c>
+      <c r="E109" s="20" t="s">
+        <v>309</v>
+      </c>
+      <c r="F109" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G109" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H109" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I109" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J109" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K109" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L109" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N109" s="22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="15">
+        <v>45742.761809398144</v>
+      </c>
+      <c r="B110" s="16" t="s">
+        <v>310</v>
+      </c>
+      <c r="C110" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="D110" s="16">
+        <v>2.0242853E7</v>
+      </c>
+      <c r="E110" s="16" t="s">
+        <v>311</v>
+      </c>
+      <c r="F110" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="G110" s="17">
+        <v>0.7</v>
+      </c>
+      <c r="H110" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="I110" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="J110" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K110" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="L110" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N110" s="18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="19">
+        <v>45742.77926577546</v>
+      </c>
+      <c r="B111" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="C111" s="20" t="s">
+        <v>313</v>
+      </c>
+      <c r="D111" s="20">
+        <v>2.0242564E7</v>
+      </c>
+      <c r="E111" s="20" t="s">
+        <v>314</v>
+      </c>
+      <c r="F111" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G111" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="H111" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="I111" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="J111" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K111" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="L111" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M111" s="20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="15">
+        <v>45742.871673587964</v>
+      </c>
+      <c r="B112" s="16" t="s">
+        <v>315</v>
+      </c>
+      <c r="C112" s="16" t="s">
+        <v>316</v>
+      </c>
+      <c r="D112" s="16">
+        <v>2.0242337E7</v>
+      </c>
+      <c r="E112" s="16" t="s">
+        <v>317</v>
+      </c>
+      <c r="F112" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G112" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H112" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I112" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J112" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K112" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L112" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M112" s="16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="19">
+        <v>45742.875244016206</v>
+      </c>
+      <c r="B113" s="20" t="s">
+        <v>318</v>
+      </c>
+      <c r="C113" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="D113" s="20">
+        <v>2.0225213E7</v>
+      </c>
+      <c r="E113" s="20" t="s">
+        <v>319</v>
+      </c>
+      <c r="F113" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G113" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H113" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I113" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J113" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K113" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L113" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M113" s="20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="15">
+        <v>45742.875463171295</v>
+      </c>
+      <c r="B114" s="16" t="s">
+        <v>320</v>
+      </c>
+      <c r="C114" s="16" t="s">
+        <v>321</v>
+      </c>
+      <c r="D114" s="16">
+        <v>2.0242524E7</v>
+      </c>
+      <c r="E114" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="F114" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G114" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H114" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I114" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J114" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K114" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L114" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N114" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="23">
+        <v>45742.87809140046</v>
+      </c>
+      <c r="B115" s="24" t="s">
+        <v>322</v>
+      </c>
+      <c r="C115" s="24" t="s">
+        <v>323</v>
+      </c>
+      <c r="D115" s="24">
+        <v>2.0223933E7</v>
+      </c>
+      <c r="E115" s="24" t="s">
+        <v>324</v>
+      </c>
+      <c r="F115" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="G115" s="25">
+        <v>0.1</v>
+      </c>
+      <c r="H115" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="I115" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="J115" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="K115" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="L115" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="M115" s="24" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/R/data/quiz_250324.xlsx
+++ b/R/data/quiz_250324.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="335">
   <si>
     <t>타임스탬프</t>
   </si>
@@ -986,6 +986,36 @@
   </si>
   <si>
     <t>엄지은</t>
+  </si>
+  <si>
+    <t>jihona1223@naver.com</t>
+  </si>
+  <si>
+    <t>나지호</t>
+  </si>
+  <si>
+    <t>dlxowns1220@naver.com</t>
+  </si>
+  <si>
+    <t>이태준</t>
+  </si>
+  <si>
+    <t>ssoning0315@naver.com</t>
+  </si>
+  <si>
+    <t>임소연</t>
+  </si>
+  <si>
+    <t>siyeon050217@gmail.com</t>
+  </si>
+  <si>
+    <t>이시연</t>
+  </si>
+  <si>
+    <t>junghanhee777@gmail.com</t>
+  </si>
+  <si>
+    <t>정한희</t>
   </si>
 </sst>
 </file>
@@ -1149,10 +1179,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1160,13 +1190,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1313,7 +1343,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A1:N115" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A1:N120" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="14">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -6235,43 +6265,248 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="23">
+      <c r="A115" s="19">
         <v>45742.87809140046</v>
       </c>
-      <c r="B115" s="24" t="s">
+      <c r="B115" s="20" t="s">
         <v>322</v>
       </c>
-      <c r="C115" s="24" t="s">
+      <c r="C115" s="20" t="s">
         <v>323</v>
       </c>
-      <c r="D115" s="24">
+      <c r="D115" s="20">
         <v>2.0223933E7</v>
       </c>
-      <c r="E115" s="24" t="s">
+      <c r="E115" s="20" t="s">
         <v>324</v>
       </c>
-      <c r="F115" s="24" t="s">
+      <c r="F115" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="G115" s="25">
-        <v>0.1</v>
-      </c>
-      <c r="H115" s="24" t="s">
+      <c r="G115" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H115" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="I115" s="24" t="s">
+      <c r="I115" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="J115" s="24" t="s">
+      <c r="J115" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="K115" s="24" t="s">
+      <c r="K115" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="L115" s="24" t="s">
+      <c r="L115" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="M115" s="24" t="s">
+      <c r="M115" s="20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="15">
+        <v>45742.896452534726</v>
+      </c>
+      <c r="B116" s="16" t="s">
+        <v>325</v>
+      </c>
+      <c r="C116" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D116" s="16">
+        <v>2.0222318E7</v>
+      </c>
+      <c r="E116" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="F116" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G116" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H116" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="I116" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="J116" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K116" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="L116" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M116" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="19">
+        <v>45742.8970958912</v>
+      </c>
+      <c r="B117" s="20" t="s">
+        <v>327</v>
+      </c>
+      <c r="C117" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D117" s="20">
+        <v>2.0223023E7</v>
+      </c>
+      <c r="E117" s="20" t="s">
+        <v>328</v>
+      </c>
+      <c r="F117" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G117" s="21">
+        <v>0.9</v>
+      </c>
+      <c r="H117" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="I117" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="J117" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K117" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="L117" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N117" s="22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="15">
+        <v>45742.897263067134</v>
+      </c>
+      <c r="B118" s="16" t="s">
+        <v>329</v>
+      </c>
+      <c r="C118" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="D118" s="16">
+        <v>2.0212838E7</v>
+      </c>
+      <c r="E118" s="16" t="s">
+        <v>330</v>
+      </c>
+      <c r="F118" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G118" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="H118" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="I118" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J118" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K118" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L118" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N118" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="19">
+        <v>45742.90298583334</v>
+      </c>
+      <c r="B119" s="20" t="s">
+        <v>331</v>
+      </c>
+      <c r="C119" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="D119" s="20">
+        <v>2.0243531E7</v>
+      </c>
+      <c r="E119" s="20" t="s">
+        <v>332</v>
+      </c>
+      <c r="F119" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G119" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H119" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I119" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J119" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K119" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L119" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N119" s="22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="23">
+        <v>45742.92465015047</v>
+      </c>
+      <c r="B120" s="24" t="s">
+        <v>333</v>
+      </c>
+      <c r="C120" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="D120" s="24">
+        <v>2.0242136E7</v>
+      </c>
+      <c r="E120" s="24" t="s">
+        <v>334</v>
+      </c>
+      <c r="F120" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="G120" s="25">
+        <v>0.1</v>
+      </c>
+      <c r="H120" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="I120" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="J120" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="K120" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="L120" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="M120" s="24" t="s">
         <v>38</v>
       </c>
     </row>

--- a/R/data/quiz_250324.xlsx
+++ b/R/data/quiz_250324.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1504" uniqueCount="403">
   <si>
     <t>타임스탬프</t>
   </si>
@@ -1016,6 +1016,210 @@
   </si>
   <si>
     <t>정한희</t>
+  </si>
+  <si>
+    <t>won00814@naver.com</t>
+  </si>
+  <si>
+    <t>사회복지학전공</t>
+  </si>
+  <si>
+    <t>이혜원</t>
+  </si>
+  <si>
+    <t>ks66248216@gmail.com</t>
+  </si>
+  <si>
+    <t>반도체디스플레이 스쿨</t>
+  </si>
+  <si>
+    <t>이재령</t>
+  </si>
+  <si>
+    <t>wldn2756@naver.com</t>
+  </si>
+  <si>
+    <t>박지우</t>
+  </si>
+  <si>
+    <t>limsa3173@gmail.com</t>
+  </si>
+  <si>
+    <t>임승언</t>
+  </si>
+  <si>
+    <t>yunseok3267@naver.com</t>
+  </si>
+  <si>
+    <t>이윤석</t>
+  </si>
+  <si>
+    <t>dmsak0708@naver.com</t>
+  </si>
+  <si>
+    <t>콘텐츠IT</t>
+  </si>
+  <si>
+    <t>최은임</t>
+  </si>
+  <si>
+    <t>hanyung1236@gmail.com</t>
+  </si>
+  <si>
+    <t>AI의료융합</t>
+  </si>
+  <si>
+    <t>한영석</t>
+  </si>
+  <si>
+    <t>dongyeon7220@gmail.com</t>
+  </si>
+  <si>
+    <t>김동연</t>
+  </si>
+  <si>
+    <t>kimjnuadad@naver.com</t>
+  </si>
+  <si>
+    <t>김도연</t>
+  </si>
+  <si>
+    <t>a01063579093@gmail.com</t>
+  </si>
+  <si>
+    <t>권민정</t>
+  </si>
+  <si>
+    <t>joonhyukkim13@gmail.com</t>
+  </si>
+  <si>
+    <t>김준혁</t>
+  </si>
+  <si>
+    <t>wjsskan13@naver.com</t>
+  </si>
+  <si>
+    <t>정치행정</t>
+  </si>
+  <si>
+    <t>전나무</t>
+  </si>
+  <si>
+    <t>hyuk7515@naver.com</t>
+  </si>
+  <si>
+    <t>김동혁</t>
+  </si>
+  <si>
+    <t>kimjw030112@naver.com</t>
+  </si>
+  <si>
+    <t>김종우</t>
+  </si>
+  <si>
+    <t>knw010211@gmail.com</t>
+  </si>
+  <si>
+    <t>김남우</t>
+  </si>
+  <si>
+    <t>xeoxeoy@naver.com</t>
+  </si>
+  <si>
+    <t>미디어스쿨</t>
+  </si>
+  <si>
+    <t>임서영</t>
+  </si>
+  <si>
+    <t>yhb2415199@gmail.com</t>
+  </si>
+  <si>
+    <t>바이오메디컬</t>
+  </si>
+  <si>
+    <t>유효빈</t>
+  </si>
+  <si>
+    <t>htkhwan@naver.com</t>
+  </si>
+  <si>
+    <t>김성민</t>
+  </si>
+  <si>
+    <t>coreabulls1@gmill.com</t>
+  </si>
+  <si>
+    <t>최성준</t>
+  </si>
+  <si>
+    <t>vmin13@naver.com</t>
+  </si>
+  <si>
+    <t>강서연</t>
+  </si>
+  <si>
+    <t>kimdongkyun1108@gmail.com</t>
+  </si>
+  <si>
+    <t>김동균</t>
+  </si>
+  <si>
+    <t>yeon2760@naver.com</t>
+  </si>
+  <si>
+    <t>강나연</t>
+  </si>
+  <si>
+    <t>seo020815@naver.com</t>
+  </si>
+  <si>
+    <t>김준서</t>
+  </si>
+  <si>
+    <t>yyeon0425@gmail.com</t>
+  </si>
+  <si>
+    <t>김연우</t>
+  </si>
+  <si>
+    <t>pcy050122@naver.com</t>
+  </si>
+  <si>
+    <t>박채영</t>
+  </si>
+  <si>
+    <t>minjj0918@naver.com</t>
+  </si>
+  <si>
+    <t>조석훈</t>
+  </si>
+  <si>
+    <t>dbawectb26@naver.com</t>
+  </si>
+  <si>
+    <t>융합신소재공학전공</t>
+  </si>
+  <si>
+    <t>서동찬</t>
+  </si>
+  <si>
+    <t>hsb2757@naver.com</t>
+  </si>
+  <si>
+    <t>허승빈</t>
+  </si>
+  <si>
+    <t>sjo47926@gmail.com</t>
+  </si>
+  <si>
+    <t>조서현</t>
+  </si>
+  <si>
+    <t>yewon0311_@naver.com</t>
+  </si>
+  <si>
+    <t>김예원</t>
   </si>
 </sst>
 </file>
@@ -1343,7 +1547,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A1:N120" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A1:N150" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="14">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -6470,43 +6674,1273 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="23">
+      <c r="A120" s="15">
         <v>45742.92465015047</v>
       </c>
-      <c r="B120" s="24" t="s">
+      <c r="B120" s="16" t="s">
         <v>333</v>
       </c>
-      <c r="C120" s="24" t="s">
+      <c r="C120" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="D120" s="24">
+      <c r="D120" s="16">
         <v>2.0242136E7</v>
       </c>
-      <c r="E120" s="24" t="s">
+      <c r="E120" s="16" t="s">
         <v>334</v>
       </c>
-      <c r="F120" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="G120" s="25">
-        <v>0.1</v>
-      </c>
-      <c r="H120" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="I120" s="24" t="s">
+      <c r="F120" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G120" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H120" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I120" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="J120" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="K120" s="24" t="s">
+      <c r="J120" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K120" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="L120" s="24" t="s">
+      <c r="L120" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="M120" s="24" t="s">
+      <c r="M120" s="16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="19">
+        <v>45742.95634793982</v>
+      </c>
+      <c r="B121" s="20" t="s">
+        <v>335</v>
+      </c>
+      <c r="C121" s="20" t="s">
+        <v>336</v>
+      </c>
+      <c r="D121" s="20">
+        <v>2.0242345E7</v>
+      </c>
+      <c r="E121" s="20" t="s">
+        <v>337</v>
+      </c>
+      <c r="F121" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G121" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H121" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I121" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="J121" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K121" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="L121" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N121" s="22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="15">
+        <v>45742.9625529051</v>
+      </c>
+      <c r="B122" s="16" t="s">
+        <v>338</v>
+      </c>
+      <c r="C122" s="16" t="s">
+        <v>339</v>
+      </c>
+      <c r="D122" s="16">
+        <v>2.0223336E7</v>
+      </c>
+      <c r="E122" s="16" t="s">
+        <v>340</v>
+      </c>
+      <c r="F122" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G122" s="17">
+        <v>0.9</v>
+      </c>
+      <c r="H122" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="I122" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="J122" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K122" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="L122" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N122" s="18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="19">
+        <v>45742.96882197917</v>
+      </c>
+      <c r="B123" s="20" t="s">
+        <v>341</v>
+      </c>
+      <c r="C123" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="D123" s="20">
+        <v>2.0221038E7</v>
+      </c>
+      <c r="E123" s="20" t="s">
+        <v>342</v>
+      </c>
+      <c r="F123" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G123" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H123" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I123" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J123" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K123" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L123" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M123" s="20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="15">
+        <v>45742.96991181713</v>
+      </c>
+      <c r="B124" s="16" t="s">
+        <v>343</v>
+      </c>
+      <c r="C124" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="D124" s="16">
+        <v>2.0226281E7</v>
+      </c>
+      <c r="E124" s="16" t="s">
+        <v>344</v>
+      </c>
+      <c r="F124" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G124" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H124" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I124" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="J124" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K124" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L124" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N124" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="19">
+        <v>45742.97525539352</v>
+      </c>
+      <c r="B125" s="20" t="s">
+        <v>345</v>
+      </c>
+      <c r="C125" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D125" s="20">
+        <v>2.0203014E7</v>
+      </c>
+      <c r="E125" s="20" t="s">
+        <v>346</v>
+      </c>
+      <c r="F125" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G125" s="21">
+        <v>0.7</v>
+      </c>
+      <c r="H125" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="I125" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="J125" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K125" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="L125" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N125" s="22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="15">
+        <v>45743.09579425926</v>
+      </c>
+      <c r="B126" s="16" t="s">
+        <v>347</v>
+      </c>
+      <c r="C126" s="16" t="s">
+        <v>348</v>
+      </c>
+      <c r="D126" s="16">
+        <v>2.0225268E7</v>
+      </c>
+      <c r="E126" s="16" t="s">
+        <v>349</v>
+      </c>
+      <c r="F126" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="G126" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H126" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="I126" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J126" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K126" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L126" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M126" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="19">
+        <v>45743.42191233796</v>
+      </c>
+      <c r="B127" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="C127" s="20" t="s">
+        <v>351</v>
+      </c>
+      <c r="D127" s="20">
+        <v>2.0226788E7</v>
+      </c>
+      <c r="E127" s="20" t="s">
+        <v>352</v>
+      </c>
+      <c r="F127" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G127" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="H127" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I127" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="J127" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="K127" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="L127" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N127" s="22" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="15">
+        <v>45743.43197423611</v>
+      </c>
+      <c r="B128" s="16" t="s">
+        <v>353</v>
+      </c>
+      <c r="C128" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="D128" s="16">
+        <v>2.024691E7</v>
+      </c>
+      <c r="E128" s="16" t="s">
+        <v>354</v>
+      </c>
+      <c r="F128" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="G128" s="17">
+        <v>0.9</v>
+      </c>
+      <c r="H128" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="I128" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="J128" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K128" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="L128" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M128" s="16" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="19">
+        <v>45743.49172755787</v>
+      </c>
+      <c r="B129" s="20" t="s">
+        <v>355</v>
+      </c>
+      <c r="C129" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="D129" s="20">
+        <v>2.0241201E7</v>
+      </c>
+      <c r="E129" s="20" t="s">
+        <v>356</v>
+      </c>
+      <c r="F129" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G129" s="21">
+        <v>0.9</v>
+      </c>
+      <c r="H129" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="I129" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="J129" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K129" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="L129" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M129" s="20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="15">
+        <v>45743.54169219907</v>
+      </c>
+      <c r="B130" s="16" t="s">
+        <v>357</v>
+      </c>
+      <c r="C130" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D130" s="16">
+        <v>2.0241506E7</v>
+      </c>
+      <c r="E130" s="16" t="s">
+        <v>358</v>
+      </c>
+      <c r="F130" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G130" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H130" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="I130" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J130" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K130" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="L130" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N130" s="18" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="19">
+        <v>45743.557255567124</v>
+      </c>
+      <c r="B131" s="20" t="s">
+        <v>359</v>
+      </c>
+      <c r="C131" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="D131" s="20">
+        <v>2.0201207E7</v>
+      </c>
+      <c r="E131" s="20" t="s">
+        <v>360</v>
+      </c>
+      <c r="F131" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G131" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H131" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I131" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J131" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K131" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L131" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N131" s="22" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="15">
+        <v>45743.567842233795</v>
+      </c>
+      <c r="B132" s="16" t="s">
+        <v>361</v>
+      </c>
+      <c r="C132" s="16" t="s">
+        <v>362</v>
+      </c>
+      <c r="D132" s="16">
+        <v>2.0242432E7</v>
+      </c>
+      <c r="E132" s="16" t="s">
+        <v>363</v>
+      </c>
+      <c r="F132" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G132" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H132" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I132" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J132" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K132" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L132" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N132" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="19">
+        <v>45743.60926409722</v>
+      </c>
+      <c r="B133" s="20" t="s">
+        <v>364</v>
+      </c>
+      <c r="C133" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="D133" s="20">
+        <v>2.0224103E7</v>
+      </c>
+      <c r="E133" s="20" t="s">
+        <v>365</v>
+      </c>
+      <c r="F133" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="G133" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="H133" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I133" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J133" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K133" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="L133" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N133" s="22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="15">
+        <v>45743.61110332176</v>
+      </c>
+      <c r="B134" s="16" t="s">
+        <v>366</v>
+      </c>
+      <c r="C134" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="D134" s="16">
+        <v>2.022411E7</v>
+      </c>
+      <c r="E134" s="16" t="s">
+        <v>367</v>
+      </c>
+      <c r="F134" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G134" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H134" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I134" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J134" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K134" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L134" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M134" s="16" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="19">
+        <v>45743.65314248843</v>
+      </c>
+      <c r="B135" s="20" t="s">
+        <v>368</v>
+      </c>
+      <c r="C135" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="D135" s="20">
+        <v>2.0202405E7</v>
+      </c>
+      <c r="E135" s="20" t="s">
+        <v>369</v>
+      </c>
+      <c r="F135" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G135" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H135" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I135" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J135" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K135" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L135" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N135" s="22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="15">
+        <v>45743.700300173616</v>
+      </c>
+      <c r="B136" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="C136" s="16" t="s">
+        <v>371</v>
+      </c>
+      <c r="D136" s="16">
+        <v>2.0252569E7</v>
+      </c>
+      <c r="E136" s="16" t="s">
+        <v>372</v>
+      </c>
+      <c r="F136" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G136" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H136" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I136" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="J136" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K136" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L136" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M136" s="16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="19">
+        <v>45743.70296239584</v>
+      </c>
+      <c r="B137" s="20" t="s">
+        <v>373</v>
+      </c>
+      <c r="C137" s="20" t="s">
+        <v>374</v>
+      </c>
+      <c r="D137" s="20">
+        <v>2.0203632E7</v>
+      </c>
+      <c r="E137" s="20" t="s">
+        <v>375</v>
+      </c>
+      <c r="F137" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="G137" s="21">
+        <v>0.7</v>
+      </c>
+      <c r="H137" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="I137" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J137" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K137" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="L137" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N137" s="22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="15">
+        <v>45743.72781268519</v>
+      </c>
+      <c r="B138" s="16" t="s">
+        <v>376</v>
+      </c>
+      <c r="C138" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="D138" s="16">
+        <v>2.0214109E7</v>
+      </c>
+      <c r="E138" s="16" t="s">
+        <v>377</v>
+      </c>
+      <c r="F138" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G138" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H138" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I138" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="J138" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K138" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="L138" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M138" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="19">
+        <v>45743.76771859954</v>
+      </c>
+      <c r="B139" s="20" t="s">
+        <v>378</v>
+      </c>
+      <c r="C139" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="D139" s="20">
+        <v>2.0242137E7</v>
+      </c>
+      <c r="E139" s="20" t="s">
+        <v>379</v>
+      </c>
+      <c r="F139" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="G139" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="H139" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="I139" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="J139" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="K139" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="L139" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N139" s="22" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="15">
+        <v>45743.77259625</v>
+      </c>
+      <c r="B140" s="16" t="s">
+        <v>380</v>
+      </c>
+      <c r="C140" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="D140" s="16">
+        <v>2.0242601E7</v>
+      </c>
+      <c r="E140" s="16" t="s">
+        <v>381</v>
+      </c>
+      <c r="F140" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G140" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H140" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I140" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J140" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K140" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L140" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M140" s="16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="19">
+        <v>45743.775762986115</v>
+      </c>
+      <c r="B141" s="20" t="s">
+        <v>382</v>
+      </c>
+      <c r="C141" s="20" t="s">
+        <v>221</v>
+      </c>
+      <c r="D141" s="20">
+        <v>2.023512E7</v>
+      </c>
+      <c r="E141" s="20" t="s">
+        <v>383</v>
+      </c>
+      <c r="F141" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G141" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H141" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I141" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J141" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K141" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="L141" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M141" s="20" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="15">
+        <v>45743.784012627315</v>
+      </c>
+      <c r="B142" s="16" t="s">
+        <v>384</v>
+      </c>
+      <c r="C142" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D142" s="16">
+        <v>2.0233901E7</v>
+      </c>
+      <c r="E142" s="16" t="s">
+        <v>385</v>
+      </c>
+      <c r="F142" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G142" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H142" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I142" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J142" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K142" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L142" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M142" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="19">
+        <v>45743.78758153935</v>
+      </c>
+      <c r="B143" s="20" t="s">
+        <v>386</v>
+      </c>
+      <c r="C143" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="D143" s="20">
+        <v>2.0215135E7</v>
+      </c>
+      <c r="E143" s="20" t="s">
+        <v>387</v>
+      </c>
+      <c r="F143" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G143" s="21">
+        <v>0.7</v>
+      </c>
+      <c r="H143" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I143" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="J143" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K143" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="L143" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N143" s="22" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="15">
+        <v>45743.827016967596</v>
+      </c>
+      <c r="B144" s="16" t="s">
+        <v>388</v>
+      </c>
+      <c r="C144" s="16" t="s">
+        <v>313</v>
+      </c>
+      <c r="D144" s="16">
+        <v>2.0232517E7</v>
+      </c>
+      <c r="E144" s="16" t="s">
+        <v>389</v>
+      </c>
+      <c r="F144" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G144" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H144" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I144" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J144" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K144" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L144" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N144" s="18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="19">
+        <v>45743.83417783565</v>
+      </c>
+      <c r="B145" s="20" t="s">
+        <v>390</v>
+      </c>
+      <c r="C145" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="D145" s="20">
+        <v>2.0243411E7</v>
+      </c>
+      <c r="E145" s="20" t="s">
+        <v>391</v>
+      </c>
+      <c r="F145" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G145" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H145" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I145" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J145" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K145" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L145" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M145" s="20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="15">
+        <v>45743.84086582176</v>
+      </c>
+      <c r="B146" s="16" t="s">
+        <v>392</v>
+      </c>
+      <c r="C146" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="D146" s="16">
+        <v>2.0246777E7</v>
+      </c>
+      <c r="E146" s="16" t="s">
+        <v>393</v>
+      </c>
+      <c r="F146" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G146" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H146" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I146" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J146" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K146" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L146" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N146" s="18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="19">
+        <v>45743.87271549768</v>
+      </c>
+      <c r="B147" s="20" t="s">
+        <v>394</v>
+      </c>
+      <c r="C147" s="20" t="s">
+        <v>395</v>
+      </c>
+      <c r="D147" s="20">
+        <v>2.0241716E7</v>
+      </c>
+      <c r="E147" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="F147" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="G147" s="21">
+        <v>0.9</v>
+      </c>
+      <c r="H147" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I147" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J147" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K147" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="L147" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M147" s="20" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="15">
+        <v>45743.90900179398</v>
+      </c>
+      <c r="B148" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="C148" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="D148" s="16">
+        <v>2.0222437E7</v>
+      </c>
+      <c r="E148" s="16" t="s">
+        <v>398</v>
+      </c>
+      <c r="F148" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G148" s="17">
+        <v>0.9</v>
+      </c>
+      <c r="H148" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="I148" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="J148" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="K148" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="L148" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M148" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="19">
+        <v>45743.92463678241</v>
+      </c>
+      <c r="B149" s="20" t="s">
+        <v>399</v>
+      </c>
+      <c r="C149" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="D149" s="20">
+        <v>2.0243842E7</v>
+      </c>
+      <c r="E149" s="20" t="s">
+        <v>400</v>
+      </c>
+      <c r="F149" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G149" s="21">
+        <v>0.7</v>
+      </c>
+      <c r="H149" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I149" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="J149" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K149" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="L149" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M149" s="20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="23">
+        <v>45743.936877500004</v>
+      </c>
+      <c r="B150" s="24" t="s">
+        <v>401</v>
+      </c>
+      <c r="C150" s="24" t="s">
+        <v>313</v>
+      </c>
+      <c r="D150" s="24">
+        <v>2.0221706E7</v>
+      </c>
+      <c r="E150" s="24" t="s">
+        <v>402</v>
+      </c>
+      <c r="F150" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="G150" s="25">
+        <v>0.1</v>
+      </c>
+      <c r="H150" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="I150" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="J150" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="K150" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="L150" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="M150" s="24" t="s">
         <v>38</v>
       </c>
     </row>

--- a/R/data/quiz_250324.xlsx
+++ b/R/data/quiz_250324.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1504" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1934" uniqueCount="502">
   <si>
     <t>타임스탬프</t>
   </si>
@@ -1220,6 +1220,303 @@
   </si>
   <si>
     <t>김예원</t>
+  </si>
+  <si>
+    <t>eugenechloek@gmail.com</t>
+  </si>
+  <si>
+    <t>권유진</t>
+  </si>
+  <si>
+    <t>dytpq0823@naver.com</t>
+  </si>
+  <si>
+    <t>이한울</t>
+  </si>
+  <si>
+    <t>tengentoppa0641@gmail.com</t>
+  </si>
+  <si>
+    <t>이정민</t>
+  </si>
+  <si>
+    <t>aod1574@naver.com</t>
+  </si>
+  <si>
+    <t>맹은지</t>
+  </si>
+  <si>
+    <t>msj5777@naver.com</t>
+  </si>
+  <si>
+    <t>마수정</t>
+  </si>
+  <si>
+    <t>llrkhn11@naver.con</t>
+  </si>
+  <si>
+    <t>임가현</t>
+  </si>
+  <si>
+    <t>kmhhth5@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">체육학과 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">최진호 </t>
+  </si>
+  <si>
+    <t>wkdguswns16@naver.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">경영학과 </t>
+  </si>
+  <si>
+    <t>장현준</t>
+  </si>
+  <si>
+    <t>cyw3690@gmail.com</t>
+  </si>
+  <si>
+    <t>언론방송융합미디어전공</t>
+  </si>
+  <si>
+    <t>최영우</t>
+  </si>
+  <si>
+    <t>brianbrian317@daum.net</t>
+  </si>
+  <si>
+    <t>디지털금융정보전공</t>
+  </si>
+  <si>
+    <t>김보성</t>
+  </si>
+  <si>
+    <t>cksals9364@naver.com</t>
+  </si>
+  <si>
+    <t>김찬민</t>
+  </si>
+  <si>
+    <t>skh4896@gmail.com</t>
+  </si>
+  <si>
+    <t>ai의료융합전공</t>
+  </si>
+  <si>
+    <t>박재민</t>
+  </si>
+  <si>
+    <t>ttendragoon666@gmail.com</t>
+  </si>
+  <si>
+    <t>이용우</t>
+  </si>
+  <si>
+    <t>ksy05061010@gmail.com</t>
+  </si>
+  <si>
+    <t>데이터테크전공</t>
+  </si>
+  <si>
+    <t>chan95713792@gmail.com</t>
+  </si>
+  <si>
+    <t>박찬영</t>
+  </si>
+  <si>
+    <t>hyunjoon0504@gmail.com</t>
+  </si>
+  <si>
+    <t>소프트웨어</t>
+  </si>
+  <si>
+    <t>최현준</t>
+  </si>
+  <si>
+    <t>choiy617@naver.com</t>
+  </si>
+  <si>
+    <t>철학과</t>
+  </si>
+  <si>
+    <t>최원찬</t>
+  </si>
+  <si>
+    <t>dark337006@naver.com</t>
+  </si>
+  <si>
+    <t>미디어스쿨 언론방송융합미디어</t>
+  </si>
+  <si>
+    <t>최봉근</t>
+  </si>
+  <si>
+    <t>ahyun11032@naver.com</t>
+  </si>
+  <si>
+    <t>김아현</t>
+  </si>
+  <si>
+    <t>joony1226@naver.com</t>
+  </si>
+  <si>
+    <t>콘텐츠 it</t>
+  </si>
+  <si>
+    <t>백주현</t>
+  </si>
+  <si>
+    <t>ksj040202@gmail.com</t>
+  </si>
+  <si>
+    <t>권수정</t>
+  </si>
+  <si>
+    <t>cara0070322@gmail.com</t>
+  </si>
+  <si>
+    <t>신성민</t>
+  </si>
+  <si>
+    <t>jsy40394725@gmail.com</t>
+  </si>
+  <si>
+    <t>조선영</t>
+  </si>
+  <si>
+    <t>8073sun@naver.com</t>
+  </si>
+  <si>
+    <t>이윤선</t>
+  </si>
+  <si>
+    <t>scb0897@naver.com</t>
+  </si>
+  <si>
+    <t>신채빈</t>
+  </si>
+  <si>
+    <t>jihyunkim917@gmail.com</t>
+  </si>
+  <si>
+    <t>김지현</t>
+  </si>
+  <si>
+    <t>shin19980527@gmail.com</t>
+  </si>
+  <si>
+    <t>신재헌</t>
+  </si>
+  <si>
+    <t>angel1004jpj@naver.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">국어국문학과 </t>
+  </si>
+  <si>
+    <t>전평지</t>
+  </si>
+  <si>
+    <t>ncc07291@naver.com</t>
+  </si>
+  <si>
+    <t>신기재</t>
+  </si>
+  <si>
+    <t>yourmylife00@naver.com</t>
+  </si>
+  <si>
+    <t>허윤진</t>
+  </si>
+  <si>
+    <t>jeonguijin45@gmail.com</t>
+  </si>
+  <si>
+    <t>데이터사이언스학과</t>
+  </si>
+  <si>
+    <t>정의진</t>
+  </si>
+  <si>
+    <t>ehdwo3325@naver.com</t>
+  </si>
+  <si>
+    <t>이동재</t>
+  </si>
+  <si>
+    <t>kass3210@naver.com</t>
+  </si>
+  <si>
+    <t>박대광</t>
+  </si>
+  <si>
+    <t>linaeun2004@naver.com</t>
+  </si>
+  <si>
+    <t>dlalswn221@naver.com</t>
+  </si>
+  <si>
+    <t>이민주</t>
+  </si>
+  <si>
+    <t>gkaehdwn68@naver.com</t>
+  </si>
+  <si>
+    <t>디지털미디어콘탠츠</t>
+  </si>
+  <si>
+    <t>함동주</t>
+  </si>
+  <si>
+    <t>spino0908@naver.com</t>
+  </si>
+  <si>
+    <t>구현우</t>
+  </si>
+  <si>
+    <t>qkrtjsdn0904@naver.com</t>
+  </si>
+  <si>
+    <t>스마트iot</t>
+  </si>
+  <si>
+    <t>박선우</t>
+  </si>
+  <si>
+    <t>seunggu4500@gmail.com</t>
+  </si>
+  <si>
+    <t>데이터사이언스</t>
+  </si>
+  <si>
+    <t>김승구</t>
+  </si>
+  <si>
+    <t>geuna7411@gmail.com</t>
+  </si>
+  <si>
+    <t>박근아</t>
+  </si>
+  <si>
+    <t>autumngo77@gmail.com</t>
+  </si>
+  <si>
+    <t>고나영</t>
+  </si>
+  <si>
+    <t>s82852747@gmail.com</t>
+  </si>
+  <si>
+    <t>서재영</t>
+  </si>
+  <si>
+    <t>idhyunmook@gmail.com</t>
+  </si>
+  <si>
+    <t>강현묵</t>
   </si>
 </sst>
 </file>
@@ -1250,7 +1547,7 @@
       <patternFill patternType="lightGray"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border/>
     <border>
       <left style="thin">
@@ -1383,10 +1680,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1394,13 +1691,27 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF442F65"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFF8F9FA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF442F65"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1410,7 +1721,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1489,6 +1800,9 @@
     <xf borderId="11" fillId="0" fontId="1" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="12" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -1547,7 +1861,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A1:N150" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A1:N193" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="14">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -7904,44 +8218,1807 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="23">
+      <c r="A150" s="15">
         <v>45743.936877500004</v>
       </c>
-      <c r="B150" s="24" t="s">
+      <c r="B150" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="C150" s="24" t="s">
+      <c r="C150" s="16" t="s">
         <v>313</v>
       </c>
-      <c r="D150" s="24">
+      <c r="D150" s="16">
         <v>2.0221706E7</v>
       </c>
-      <c r="E150" s="24" t="s">
+      <c r="E150" s="16" t="s">
         <v>402</v>
       </c>
-      <c r="F150" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="G150" s="25">
-        <v>0.1</v>
-      </c>
-      <c r="H150" s="24" t="s">
+      <c r="F150" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G150" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H150" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="I150" s="24" t="s">
+      <c r="I150" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="J150" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="K150" s="24" t="s">
+      <c r="J150" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K150" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="L150" s="24" t="s">
+      <c r="L150" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="M150" s="24" t="s">
+      <c r="M150" s="16" t="s">
         <v>38</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="19">
+        <v>45743.969758935185</v>
+      </c>
+      <c r="B151" s="20" t="s">
+        <v>403</v>
+      </c>
+      <c r="C151" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="D151" s="20">
+        <v>2.0221204E7</v>
+      </c>
+      <c r="E151" s="20" t="s">
+        <v>404</v>
+      </c>
+      <c r="F151" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G151" s="21">
+        <v>0.7</v>
+      </c>
+      <c r="H151" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I151" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J151" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K151" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L151" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N151" s="22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="15">
+        <v>45744.12257310185</v>
+      </c>
+      <c r="B152" s="16" t="s">
+        <v>405</v>
+      </c>
+      <c r="C152" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D152" s="16">
+        <v>2.0253018E7</v>
+      </c>
+      <c r="E152" s="16" t="s">
+        <v>406</v>
+      </c>
+      <c r="F152" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G152" s="17">
+        <v>0.7</v>
+      </c>
+      <c r="H152" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="I152" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="J152" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K152" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="L152" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M152" s="16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="19">
+        <v>45744.12526078704</v>
+      </c>
+      <c r="B153" s="20" t="s">
+        <v>407</v>
+      </c>
+      <c r="C153" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="D153" s="20">
+        <v>2.0241629E7</v>
+      </c>
+      <c r="E153" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="F153" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G153" s="21">
+        <v>0.7</v>
+      </c>
+      <c r="H153" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="I153" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="J153" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="K153" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="L153" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N153" s="22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="15">
+        <v>45744.182211238425</v>
+      </c>
+      <c r="B154" s="16" t="s">
+        <v>409</v>
+      </c>
+      <c r="C154" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D154" s="16">
+        <v>2.0232949E7</v>
+      </c>
+      <c r="E154" s="16" t="s">
+        <v>410</v>
+      </c>
+      <c r="F154" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G154" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H154" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I154" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J154" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K154" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L154" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M154" s="16" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="19">
+        <v>45744.35175047454</v>
+      </c>
+      <c r="B155" s="20" t="s">
+        <v>411</v>
+      </c>
+      <c r="C155" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="D155" s="20">
+        <v>2.023708E7</v>
+      </c>
+      <c r="E155" s="20" t="s">
+        <v>412</v>
+      </c>
+      <c r="F155" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G155" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H155" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I155" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J155" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K155" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L155" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M155" s="20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="15">
+        <v>45744.43492325232</v>
+      </c>
+      <c r="B156" s="16" t="s">
+        <v>413</v>
+      </c>
+      <c r="C156" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D156" s="16">
+        <v>2.0243943E7</v>
+      </c>
+      <c r="E156" s="16" t="s">
+        <v>414</v>
+      </c>
+      <c r="F156" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G156" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H156" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I156" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J156" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K156" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L156" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M156" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="19">
+        <v>45744.46464284722</v>
+      </c>
+      <c r="B157" s="20" t="s">
+        <v>415</v>
+      </c>
+      <c r="C157" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="D157" s="20">
+        <v>2.024415E7</v>
+      </c>
+      <c r="E157" s="20" t="s">
+        <v>417</v>
+      </c>
+      <c r="F157" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="G157" s="21">
+        <v>0.9</v>
+      </c>
+      <c r="H157" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="I157" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J157" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K157" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L157" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M157" s="20" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="15">
+        <v>45744.49144719908</v>
+      </c>
+      <c r="B158" s="16" t="s">
+        <v>418</v>
+      </c>
+      <c r="C158" s="16" t="s">
+        <v>419</v>
+      </c>
+      <c r="D158" s="16">
+        <v>2.0213033E7</v>
+      </c>
+      <c r="E158" s="16" t="s">
+        <v>420</v>
+      </c>
+      <c r="F158" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G158" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="H158" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="I158" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="J158" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="K158" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="L158" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M158" s="16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="19">
+        <v>45744.49462819444</v>
+      </c>
+      <c r="B159" s="20" t="s">
+        <v>421</v>
+      </c>
+      <c r="C159" s="20" t="s">
+        <v>422</v>
+      </c>
+      <c r="D159" s="20">
+        <v>2.0242581E7</v>
+      </c>
+      <c r="E159" s="20" t="s">
+        <v>423</v>
+      </c>
+      <c r="F159" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="G159" s="21">
+        <v>0.7</v>
+      </c>
+      <c r="H159" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="I159" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J159" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K159" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="L159" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M159" s="20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="15">
+        <v>45744.49682170139</v>
+      </c>
+      <c r="B160" s="16" t="s">
+        <v>424</v>
+      </c>
+      <c r="C160" s="16" t="s">
+        <v>425</v>
+      </c>
+      <c r="D160" s="16">
+        <v>2.0243209E7</v>
+      </c>
+      <c r="E160" s="16" t="s">
+        <v>426</v>
+      </c>
+      <c r="F160" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G160" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="H160" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="I160" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="J160" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K160" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="L160" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N160" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="19">
+        <v>45744.49818112269</v>
+      </c>
+      <c r="B161" s="20" t="s">
+        <v>427</v>
+      </c>
+      <c r="C161" s="20" t="s">
+        <v>351</v>
+      </c>
+      <c r="D161" s="20">
+        <v>2.0226726E7</v>
+      </c>
+      <c r="E161" s="20" t="s">
+        <v>428</v>
+      </c>
+      <c r="F161" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G161" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H161" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I161" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="J161" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K161" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L161" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M161" s="20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="15">
+        <v>45744.49821899306</v>
+      </c>
+      <c r="B162" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="C162" s="16" t="s">
+        <v>430</v>
+      </c>
+      <c r="D162" s="16">
+        <v>2.02216743E8</v>
+      </c>
+      <c r="E162" s="16" t="s">
+        <v>431</v>
+      </c>
+      <c r="F162" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G162" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H162" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I162" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="J162" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K162" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L162" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M162" s="16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="19">
+        <v>45744.521570937504</v>
+      </c>
+      <c r="B163" s="20" t="s">
+        <v>432</v>
+      </c>
+      <c r="C163" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="D163" s="20">
+        <v>2.022163E7</v>
+      </c>
+      <c r="E163" s="20" t="s">
+        <v>433</v>
+      </c>
+      <c r="F163" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G163" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H163" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I163" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J163" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K163" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="L163" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M163" s="20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="15">
+        <v>45744.52257002315</v>
+      </c>
+      <c r="B164" s="16" t="s">
+        <v>434</v>
+      </c>
+      <c r="C164" s="16" t="s">
+        <v>435</v>
+      </c>
+      <c r="D164" s="16">
+        <v>2.0243202E7</v>
+      </c>
+      <c r="E164" s="16" t="s">
+        <v>381</v>
+      </c>
+      <c r="F164" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G164" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H164" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I164" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J164" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K164" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L164" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M164" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="19">
+        <v>45744.53485589121</v>
+      </c>
+      <c r="B165" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="C165" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D165" s="20">
+        <v>2.0242964E7</v>
+      </c>
+      <c r="E165" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="F165" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="G165" s="21">
+        <v>0.7</v>
+      </c>
+      <c r="H165" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="I165" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J165" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K165" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="L165" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N165" s="22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="15">
+        <v>45744.57298241898</v>
+      </c>
+      <c r="B166" s="16" t="s">
+        <v>438</v>
+      </c>
+      <c r="C166" s="16" t="s">
+        <v>439</v>
+      </c>
+      <c r="D166" s="16">
+        <v>2.0255271E7</v>
+      </c>
+      <c r="E166" s="16" t="s">
+        <v>440</v>
+      </c>
+      <c r="F166" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G166" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H166" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I166" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J166" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K166" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L166" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N166" s="18" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="19">
+        <v>45744.5875827662</v>
+      </c>
+      <c r="B167" s="20" t="s">
+        <v>441</v>
+      </c>
+      <c r="C167" s="20" t="s">
+        <v>442</v>
+      </c>
+      <c r="D167" s="20">
+        <v>2.0231097E7</v>
+      </c>
+      <c r="E167" s="20" t="s">
+        <v>443</v>
+      </c>
+      <c r="F167" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G167" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H167" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I167" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J167" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K167" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L167" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M167" s="20" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="15">
+        <v>45744.60333951389</v>
+      </c>
+      <c r="B168" s="16" t="s">
+        <v>444</v>
+      </c>
+      <c r="C168" s="16" t="s">
+        <v>445</v>
+      </c>
+      <c r="D168" s="16">
+        <v>2.0202581E7</v>
+      </c>
+      <c r="E168" s="16" t="s">
+        <v>446</v>
+      </c>
+      <c r="F168" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G168" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H168" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I168" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J168" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K168" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L168" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M168" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="19">
+        <v>45744.62166983796</v>
+      </c>
+      <c r="B169" s="20" t="s">
+        <v>447</v>
+      </c>
+      <c r="C169" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="D169" s="20">
+        <v>2.0243809E7</v>
+      </c>
+      <c r="E169" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="F169" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G169" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="H169" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="I169" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="J169" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K169" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="L169" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M169" s="20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="15">
+        <v>45744.65904128472</v>
+      </c>
+      <c r="B170" s="16" t="s">
+        <v>449</v>
+      </c>
+      <c r="C170" s="16" t="s">
+        <v>450</v>
+      </c>
+      <c r="D170" s="16">
+        <v>2.0245181E7</v>
+      </c>
+      <c r="E170" s="16" t="s">
+        <v>451</v>
+      </c>
+      <c r="F170" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G170" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H170" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="I170" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J170" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K170" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L170" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M170" s="16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="19">
+        <v>45744.67719368056</v>
+      </c>
+      <c r="B171" s="20" t="s">
+        <v>452</v>
+      </c>
+      <c r="C171" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="D171" s="20">
+        <v>2.024621E7</v>
+      </c>
+      <c r="E171" s="20" t="s">
+        <v>453</v>
+      </c>
+      <c r="F171" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G171" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H171" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I171" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J171" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K171" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L171" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N171" s="22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="15">
+        <v>45744.71792326389</v>
+      </c>
+      <c r="B172" s="16" t="s">
+        <v>454</v>
+      </c>
+      <c r="C172" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="D172" s="16">
+        <v>2.024674E7</v>
+      </c>
+      <c r="E172" s="16" t="s">
+        <v>455</v>
+      </c>
+      <c r="F172" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G172" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H172" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I172" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J172" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K172" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L172" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M172" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="19">
+        <v>45744.71794564815</v>
+      </c>
+      <c r="B173" s="20" t="s">
+        <v>456</v>
+      </c>
+      <c r="C173" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="D173" s="20">
+        <v>2.0222634E7</v>
+      </c>
+      <c r="E173" s="20" t="s">
+        <v>457</v>
+      </c>
+      <c r="F173" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="G173" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="H173" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I173" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J173" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="K173" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="L173" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N173" s="22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="15">
+        <v>45744.727034791664</v>
+      </c>
+      <c r="B174" s="16" t="s">
+        <v>458</v>
+      </c>
+      <c r="C174" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="D174" s="16">
+        <v>2.0217011E7</v>
+      </c>
+      <c r="E174" s="16" t="s">
+        <v>459</v>
+      </c>
+      <c r="F174" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G174" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H174" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I174" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J174" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K174" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L174" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M174" s="16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="19">
+        <v>45744.74417159722</v>
+      </c>
+      <c r="B175" s="20" t="s">
+        <v>460</v>
+      </c>
+      <c r="C175" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="D175" s="20">
+        <v>2.0243521E7</v>
+      </c>
+      <c r="E175" s="20" t="s">
+        <v>461</v>
+      </c>
+      <c r="F175" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G175" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="H175" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I175" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="J175" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K175" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="L175" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N175" s="22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="15">
+        <v>45744.75364083333</v>
+      </c>
+      <c r="B176" s="16" t="s">
+        <v>462</v>
+      </c>
+      <c r="C176" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="D176" s="16">
+        <v>2.0241024E7</v>
+      </c>
+      <c r="E176" s="16" t="s">
+        <v>463</v>
+      </c>
+      <c r="F176" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="G176" s="17">
+        <v>0.7</v>
+      </c>
+      <c r="H176" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="I176" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J176" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K176" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="L176" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N176" s="18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="19">
+        <v>45744.75728013889</v>
+      </c>
+      <c r="B177" s="20" t="s">
+        <v>464</v>
+      </c>
+      <c r="C177" s="20" t="s">
+        <v>442</v>
+      </c>
+      <c r="D177" s="20">
+        <v>2.0171054E7</v>
+      </c>
+      <c r="E177" s="20" t="s">
+        <v>465</v>
+      </c>
+      <c r="F177" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G177" s="21">
+        <v>0.9</v>
+      </c>
+      <c r="H177" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I177" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="J177" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K177" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="L177" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M177" s="20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="15">
+        <v>45744.78984628472</v>
+      </c>
+      <c r="B178" s="16" t="s">
+        <v>466</v>
+      </c>
+      <c r="C178" s="16" t="s">
+        <v>467</v>
+      </c>
+      <c r="D178" s="16">
+        <v>2.0241087E7</v>
+      </c>
+      <c r="E178" s="16" t="s">
+        <v>468</v>
+      </c>
+      <c r="F178" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="G178" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="H178" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I178" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J178" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K178" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="L178" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N178" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="19">
+        <v>45744.80300846064</v>
+      </c>
+      <c r="B179" s="20" t="s">
+        <v>469</v>
+      </c>
+      <c r="C179" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="D179" s="20">
+        <v>2.0192216E7</v>
+      </c>
+      <c r="E179" s="20" t="s">
+        <v>470</v>
+      </c>
+      <c r="F179" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G179" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H179" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I179" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J179" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K179" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L179" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M179" s="20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="15">
+        <v>45744.84562807871</v>
+      </c>
+      <c r="B180" s="16" t="s">
+        <v>471</v>
+      </c>
+      <c r="C180" s="16" t="s">
+        <v>442</v>
+      </c>
+      <c r="D180" s="16">
+        <v>2.0221111E7</v>
+      </c>
+      <c r="E180" s="16" t="s">
+        <v>472</v>
+      </c>
+      <c r="F180" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G180" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H180" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I180" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J180" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K180" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L180" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N180" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="19">
+        <v>45744.85077452546</v>
+      </c>
+      <c r="B181" s="20" t="s">
+        <v>473</v>
+      </c>
+      <c r="C181" s="20" t="s">
+        <v>474</v>
+      </c>
+      <c r="D181" s="20">
+        <v>2.0243252E7</v>
+      </c>
+      <c r="E181" s="20" t="s">
+        <v>475</v>
+      </c>
+      <c r="F181" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G181" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H181" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I181" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J181" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K181" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="L181" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N181" s="22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="15">
+        <v>45744.85787952546</v>
+      </c>
+      <c r="B182" s="16" t="s">
+        <v>476</v>
+      </c>
+      <c r="C182" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="D182" s="16">
+        <v>2.0222556E7</v>
+      </c>
+      <c r="E182" s="16" t="s">
+        <v>477</v>
+      </c>
+      <c r="F182" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="G182" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H182" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I182" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="J182" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K182" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L182" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N182" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="19">
+        <v>45744.85875274306</v>
+      </c>
+      <c r="B183" s="20" t="s">
+        <v>478</v>
+      </c>
+      <c r="C183" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="D183" s="20">
+        <v>2.0212721E7</v>
+      </c>
+      <c r="E183" s="20" t="s">
+        <v>479</v>
+      </c>
+      <c r="F183" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G183" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H183" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I183" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="J183" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K183" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L183" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M183" s="20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="15">
+        <v>45744.90693228009</v>
+      </c>
+      <c r="B184" s="16" t="s">
+        <v>480</v>
+      </c>
+      <c r="C184" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="D184" s="16">
+        <v>2.0246272E7</v>
+      </c>
+      <c r="E184" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F184" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G184" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H184" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I184" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="J184" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K184" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L184" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N184" s="18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="19">
+        <v>45744.94627189815</v>
+      </c>
+      <c r="B185" s="20" t="s">
+        <v>481</v>
+      </c>
+      <c r="C185" s="20" t="s">
+        <v>211</v>
+      </c>
+      <c r="D185" s="20">
+        <v>2.0241066E7</v>
+      </c>
+      <c r="E185" s="20" t="s">
+        <v>482</v>
+      </c>
+      <c r="F185" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G185" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="H185" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I185" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="J185" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="K185" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L185" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N185" s="22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="15">
+        <v>45744.94761878472</v>
+      </c>
+      <c r="B186" s="16" t="s">
+        <v>483</v>
+      </c>
+      <c r="C186" s="16" t="s">
+        <v>484</v>
+      </c>
+      <c r="D186" s="16">
+        <v>2.0242587E7</v>
+      </c>
+      <c r="E186" s="16" t="s">
+        <v>485</v>
+      </c>
+      <c r="F186" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G186" s="17">
+        <v>0.7</v>
+      </c>
+      <c r="H186" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="I186" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="J186" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K186" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="L186" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N186" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="19">
+        <v>45744.97520884259</v>
+      </c>
+      <c r="B187" s="20" t="s">
+        <v>486</v>
+      </c>
+      <c r="C187" s="20" t="s">
+        <v>442</v>
+      </c>
+      <c r="D187" s="20">
+        <v>2.0211005E7</v>
+      </c>
+      <c r="E187" s="20" t="s">
+        <v>487</v>
+      </c>
+      <c r="F187" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G187" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H187" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I187" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="J187" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K187" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="L187" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M187" s="20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="15">
+        <v>45744.98871805555</v>
+      </c>
+      <c r="B188" s="16" t="s">
+        <v>488</v>
+      </c>
+      <c r="C188" s="16" t="s">
+        <v>489</v>
+      </c>
+      <c r="D188" s="16">
+        <v>2.022712E7</v>
+      </c>
+      <c r="E188" s="16" t="s">
+        <v>490</v>
+      </c>
+      <c r="F188" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G188" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="H188" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="I188" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="J188" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K188" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="L188" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M188" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="19">
+        <v>45745.06495306713</v>
+      </c>
+      <c r="B189" s="20" t="s">
+        <v>491</v>
+      </c>
+      <c r="C189" s="20" t="s">
+        <v>492</v>
+      </c>
+      <c r="D189" s="20">
+        <v>2.0243211E7</v>
+      </c>
+      <c r="E189" s="20" t="s">
+        <v>493</v>
+      </c>
+      <c r="F189" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="G189" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="H189" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="I189" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J189" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K189" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L189" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M189" s="20" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="15">
+        <v>45745.08035798611</v>
+      </c>
+      <c r="B190" s="16" t="s">
+        <v>494</v>
+      </c>
+      <c r="C190" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D190" s="16">
+        <v>2.024351E7</v>
+      </c>
+      <c r="E190" s="16" t="s">
+        <v>495</v>
+      </c>
+      <c r="F190" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G190" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H190" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I190" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J190" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K190" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L190" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N190" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="19">
+        <v>45745.08878167824</v>
+      </c>
+      <c r="B191" s="20" t="s">
+        <v>496</v>
+      </c>
+      <c r="C191" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="D191" s="20">
+        <v>2.0246605E7</v>
+      </c>
+      <c r="E191" s="20" t="s">
+        <v>497</v>
+      </c>
+      <c r="F191" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G191" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="H191" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="I191" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J191" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K191" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="L191" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N191" s="22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="15">
+        <v>45745.111754930556</v>
+      </c>
+      <c r="B192" s="16" t="s">
+        <v>498</v>
+      </c>
+      <c r="C192" s="16" t="s">
+        <v>435</v>
+      </c>
+      <c r="D192" s="16">
+        <v>2.0243226E7</v>
+      </c>
+      <c r="E192" s="16" t="s">
+        <v>499</v>
+      </c>
+      <c r="F192" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G192" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H192" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I192" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J192" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K192" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L192" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M192" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="23">
+        <v>45745.207377638886</v>
+      </c>
+      <c r="B193" s="24" t="s">
+        <v>500</v>
+      </c>
+      <c r="C193" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="D193" s="24">
+        <v>2.0214102E7</v>
+      </c>
+      <c r="E193" s="24" t="s">
+        <v>501</v>
+      </c>
+      <c r="F193" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="G193" s="25">
+        <v>0.5</v>
+      </c>
+      <c r="H193" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="I193" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="J193" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="K193" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="L193" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="N193" s="26" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/R/data/quiz_250324.xlsx
+++ b/R/data/quiz_250324.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1934" uniqueCount="502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2274" uniqueCount="580">
   <si>
     <t>타임스탬프</t>
   </si>
@@ -1517,6 +1517,240 @@
   </si>
   <si>
     <t>강현묵</t>
+  </si>
+  <si>
+    <t>ouc007@naver.com</t>
+  </si>
+  <si>
+    <t>오유찬</t>
+  </si>
+  <si>
+    <t>tmdcks0162@naver.com</t>
+  </si>
+  <si>
+    <t>김승찬</t>
+  </si>
+  <si>
+    <t>jungjimin2526@naver.com</t>
+  </si>
+  <si>
+    <t>정지민</t>
+  </si>
+  <si>
+    <t>05hg8239@naver.com</t>
+  </si>
+  <si>
+    <t>조현근</t>
+  </si>
+  <si>
+    <t>oddwhale@naver.com</t>
+  </si>
+  <si>
+    <t>글로벌비즈니스</t>
+  </si>
+  <si>
+    <t>정혜인</t>
+  </si>
+  <si>
+    <t>retmiof32145@gmail.com</t>
+  </si>
+  <si>
+    <t>권지욱</t>
+  </si>
+  <si>
+    <t>coolalex127@gmail.com</t>
+  </si>
+  <si>
+    <t>빅데이터</t>
+  </si>
+  <si>
+    <t>양윤모</t>
+  </si>
+  <si>
+    <t>hrk5353@naver.com</t>
+  </si>
+  <si>
+    <t>홍리경</t>
+  </si>
+  <si>
+    <t>kelly9845@naver.com</t>
+  </si>
+  <si>
+    <t>박서연</t>
+  </si>
+  <si>
+    <t>yuvin0612@naaver.com</t>
+  </si>
+  <si>
+    <t>장유빈</t>
+  </si>
+  <si>
+    <t>guschdl0313@gmail.com</t>
+  </si>
+  <si>
+    <t>최현종</t>
+  </si>
+  <si>
+    <t>de3230@naver.com</t>
+  </si>
+  <si>
+    <t>정대현</t>
+  </si>
+  <si>
+    <t>1991kcal@kakao.com</t>
+  </si>
+  <si>
+    <t>데이터사이언스학부 데이터테크전공</t>
+  </si>
+  <si>
+    <t>원채영</t>
+  </si>
+  <si>
+    <t>dhdhdh1010@naver.com</t>
+  </si>
+  <si>
+    <t>김도희</t>
+  </si>
+  <si>
+    <t>kid050311@naver.com</t>
+  </si>
+  <si>
+    <t>김이담</t>
+  </si>
+  <si>
+    <t>rhkrwnstjd19@gmail.com</t>
+  </si>
+  <si>
+    <t>곽준성</t>
+  </si>
+  <si>
+    <t>20223505@hallym.ac.kr</t>
+  </si>
+  <si>
+    <t>생명과학</t>
+  </si>
+  <si>
+    <t>권준성</t>
+  </si>
+  <si>
+    <t>derechos2405@gmail.com</t>
+  </si>
+  <si>
+    <t>김성훈</t>
+  </si>
+  <si>
+    <t>ggffee1129@gmail.com</t>
+  </si>
+  <si>
+    <t>ai의료(인공지능융합학부)</t>
+  </si>
+  <si>
+    <t>송관엽</t>
+  </si>
+  <si>
+    <t>taehoon9466@gmail.com</t>
+  </si>
+  <si>
+    <t>반도체-디스플레이</t>
+  </si>
+  <si>
+    <t>염태훈</t>
+  </si>
+  <si>
+    <t>chlwhddbs715@gmail.com</t>
+  </si>
+  <si>
+    <t>반도체공학과</t>
+  </si>
+  <si>
+    <t>최종윤</t>
+  </si>
+  <si>
+    <t>csu1102@naver.com</t>
+  </si>
+  <si>
+    <t>조성운</t>
+  </si>
+  <si>
+    <t>gmls3318@naver.com</t>
+  </si>
+  <si>
+    <t>변희연</t>
+  </si>
+  <si>
+    <t>0205ysm@naver.com</t>
+  </si>
+  <si>
+    <t>반도체디스플레이 학과</t>
+  </si>
+  <si>
+    <t>유승민</t>
+  </si>
+  <si>
+    <t>eunha12314@naver.com</t>
+  </si>
+  <si>
+    <t>경규남</t>
+  </si>
+  <si>
+    <t>ysj030412@gmail.com</t>
+  </si>
+  <si>
+    <t>윤성중</t>
+  </si>
+  <si>
+    <t>skdda1073@naver.com</t>
+  </si>
+  <si>
+    <t>고경완</t>
+  </si>
+  <si>
+    <t>dlrbqls0808@gmail.com</t>
+  </si>
+  <si>
+    <t>이규빈</t>
+  </si>
+  <si>
+    <t>20241726@hallym.ac.kr</t>
+  </si>
+  <si>
+    <t>이효린</t>
+  </si>
+  <si>
+    <t>angkscmzndyal@naver.com</t>
+  </si>
+  <si>
+    <t>박상재</t>
+  </si>
+  <si>
+    <t>22berthak@naver.com</t>
+  </si>
+  <si>
+    <t>글로벌비즈니스학과</t>
+  </si>
+  <si>
+    <t>강유진</t>
+  </si>
+  <si>
+    <t>jung5jung59708@gmail.com</t>
+  </si>
+  <si>
+    <t>정서현</t>
+  </si>
+  <si>
+    <t>castle@hallym.ac.kr</t>
+  </si>
+  <si>
+    <t>배은성</t>
+  </si>
+  <si>
+    <t>hyunmibob209@gmail.com</t>
+  </si>
+  <si>
+    <t>언론융합미디어</t>
+  </si>
+  <si>
+    <t>이현민</t>
   </si>
 </sst>
 </file>
@@ -1861,7 +2095,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A1:N193" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A1:N227" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="14">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -9981,43 +10215,1437 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="23">
+      <c r="A193" s="19">
         <v>45745.207377638886</v>
       </c>
-      <c r="B193" s="24" t="s">
+      <c r="B193" s="20" t="s">
         <v>500</v>
       </c>
-      <c r="C193" s="24" t="s">
+      <c r="C193" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="D193" s="24">
+      <c r="D193" s="20">
         <v>2.0214102E7</v>
       </c>
-      <c r="E193" s="24" t="s">
+      <c r="E193" s="20" t="s">
         <v>501</v>
       </c>
-      <c r="F193" s="24" t="s">
+      <c r="F193" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="G193" s="25">
+      <c r="G193" s="21">
         <v>0.5</v>
       </c>
-      <c r="H193" s="24" t="s">
+      <c r="H193" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="I193" s="24" t="s">
+      <c r="I193" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="J193" s="24" t="s">
+      <c r="J193" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="K193" s="24" t="s">
+      <c r="K193" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="L193" s="24" t="s">
+      <c r="L193" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="N193" s="26" t="s">
+      <c r="N193" s="22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="15">
+        <v>45745.38786891203</v>
+      </c>
+      <c r="B194" s="16" t="s">
+        <v>502</v>
+      </c>
+      <c r="C194" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="D194" s="16">
+        <v>2.0232831E7</v>
+      </c>
+      <c r="E194" s="16" t="s">
+        <v>503</v>
+      </c>
+      <c r="F194" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G194" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H194" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="I194" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="J194" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K194" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="L194" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M194" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="19">
+        <v>45745.44676853009</v>
+      </c>
+      <c r="B195" s="20" t="s">
+        <v>504</v>
+      </c>
+      <c r="C195" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="D195" s="20">
+        <v>2.0222713E7</v>
+      </c>
+      <c r="E195" s="20" t="s">
+        <v>505</v>
+      </c>
+      <c r="F195" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G195" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H195" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I195" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J195" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K195" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L195" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N195" s="22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="15">
+        <v>45745.45414523148</v>
+      </c>
+      <c r="B196" s="16" t="s">
+        <v>506</v>
+      </c>
+      <c r="C196" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="D196" s="16">
+        <v>2.0242841E7</v>
+      </c>
+      <c r="E196" s="16" t="s">
+        <v>507</v>
+      </c>
+      <c r="F196" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G196" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H196" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="I196" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="J196" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K196" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="L196" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M196" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="19">
+        <v>45745.477923611106</v>
+      </c>
+      <c r="B197" s="20" t="s">
+        <v>508</v>
+      </c>
+      <c r="C197" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="D197" s="20">
+        <v>2.0242438E7</v>
+      </c>
+      <c r="E197" s="20" t="s">
+        <v>509</v>
+      </c>
+      <c r="F197" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G197" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H197" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I197" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="J197" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K197" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L197" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N197" s="22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="15">
+        <v>45745.48281497685</v>
+      </c>
+      <c r="B198" s="16" t="s">
+        <v>510</v>
+      </c>
+      <c r="C198" s="16" t="s">
+        <v>511</v>
+      </c>
+      <c r="D198" s="16">
+        <v>2.0226422E7</v>
+      </c>
+      <c r="E198" s="16" t="s">
+        <v>512</v>
+      </c>
+      <c r="F198" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G198" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="H198" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I198" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="J198" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K198" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L198" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M198" s="16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="19">
+        <v>45745.537348541664</v>
+      </c>
+      <c r="B199" s="20" t="s">
+        <v>513</v>
+      </c>
+      <c r="C199" s="20" t="s">
+        <v>371</v>
+      </c>
+      <c r="D199" s="20">
+        <v>2.0242505E7</v>
+      </c>
+      <c r="E199" s="20" t="s">
+        <v>514</v>
+      </c>
+      <c r="F199" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G199" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="H199" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="I199" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J199" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K199" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="L199" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N199" s="22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="15">
+        <v>45745.577599965276</v>
+      </c>
+      <c r="B200" s="16" t="s">
+        <v>515</v>
+      </c>
+      <c r="C200" s="16" t="s">
+        <v>516</v>
+      </c>
+      <c r="D200" s="16">
+        <v>2.02052E7</v>
+      </c>
+      <c r="E200" s="16" t="s">
+        <v>517</v>
+      </c>
+      <c r="F200" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G200" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="H200" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I200" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J200" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K200" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L200" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N200" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="19">
+        <v>45745.57966354166</v>
+      </c>
+      <c r="B201" s="20" t="s">
+        <v>518</v>
+      </c>
+      <c r="C201" s="20" t="s">
+        <v>371</v>
+      </c>
+      <c r="D201" s="20">
+        <v>2.0242588E7</v>
+      </c>
+      <c r="E201" s="20" t="s">
+        <v>519</v>
+      </c>
+      <c r="F201" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G201" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H201" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I201" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J201" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K201" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L201" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N201" s="22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="15">
+        <v>45745.592280937504</v>
+      </c>
+      <c r="B202" s="16" t="s">
+        <v>520</v>
+      </c>
+      <c r="C202" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="D202" s="16">
+        <v>2.0223515E7</v>
+      </c>
+      <c r="E202" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="F202" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G202" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H202" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I202" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="J202" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K202" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="L202" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N202" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="19">
+        <v>45745.60327856481</v>
+      </c>
+      <c r="B203" s="20" t="s">
+        <v>522</v>
+      </c>
+      <c r="C203" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="D203" s="20">
+        <v>2.0203537E7</v>
+      </c>
+      <c r="E203" s="20" t="s">
+        <v>523</v>
+      </c>
+      <c r="F203" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G203" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H203" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="I203" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J203" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K203" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L203" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M203" s="20" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="15">
+        <v>45745.629095474535</v>
+      </c>
+      <c r="B204" s="16" t="s">
+        <v>524</v>
+      </c>
+      <c r="C204" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="D204" s="16">
+        <v>2.0225272E7</v>
+      </c>
+      <c r="E204" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="F204" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G204" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H204" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="I204" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J204" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K204" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="L204" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N204" s="18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="19">
+        <v>45745.66444224537</v>
+      </c>
+      <c r="B205" s="20" t="s">
+        <v>526</v>
+      </c>
+      <c r="C205" s="20" t="s">
+        <v>371</v>
+      </c>
+      <c r="D205" s="20">
+        <v>2.0243348E7</v>
+      </c>
+      <c r="E205" s="20" t="s">
+        <v>527</v>
+      </c>
+      <c r="F205" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G205" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H205" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I205" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J205" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K205" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="L205" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M205" s="20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="15">
+        <v>45745.69747666667</v>
+      </c>
+      <c r="B206" s="16" t="s">
+        <v>528</v>
+      </c>
+      <c r="C206" s="16" t="s">
+        <v>529</v>
+      </c>
+      <c r="D206" s="16">
+        <v>2.0243233E7</v>
+      </c>
+      <c r="E206" s="16" t="s">
+        <v>530</v>
+      </c>
+      <c r="F206" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G206" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="H206" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="I206" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J206" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K206" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="L206" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N206" s="18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="19">
+        <v>45745.711864282406</v>
+      </c>
+      <c r="B207" s="20" t="s">
+        <v>531</v>
+      </c>
+      <c r="C207" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="D207" s="20">
+        <v>2.0242208E7</v>
+      </c>
+      <c r="E207" s="20" t="s">
+        <v>532</v>
+      </c>
+      <c r="F207" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G207" s="21">
+        <v>0.7</v>
+      </c>
+      <c r="H207" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="I207" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="J207" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="K207" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="L207" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N207" s="22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="15">
+        <v>45745.71554230324</v>
+      </c>
+      <c r="B208" s="16" t="s">
+        <v>533</v>
+      </c>
+      <c r="C208" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="D208" s="16">
+        <v>2.0246916E7</v>
+      </c>
+      <c r="E208" s="16" t="s">
+        <v>534</v>
+      </c>
+      <c r="F208" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G208" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="H208" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="I208" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J208" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K208" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="L208" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N208" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="19">
+        <v>45745.72153609953</v>
+      </c>
+      <c r="B209" s="20" t="s">
+        <v>535</v>
+      </c>
+      <c r="C209" s="20" t="s">
+        <v>348</v>
+      </c>
+      <c r="D209" s="20">
+        <v>2.0195109E7</v>
+      </c>
+      <c r="E209" s="20" t="s">
+        <v>536</v>
+      </c>
+      <c r="F209" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G209" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H209" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I209" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J209" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K209" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L209" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M209" s="20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="15">
+        <v>45745.733114664356</v>
+      </c>
+      <c r="B210" s="16" t="s">
+        <v>537</v>
+      </c>
+      <c r="C210" s="16" t="s">
+        <v>538</v>
+      </c>
+      <c r="D210" s="16">
+        <v>2.0223505E7</v>
+      </c>
+      <c r="E210" s="16" t="s">
+        <v>539</v>
+      </c>
+      <c r="F210" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G210" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H210" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I210" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J210" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K210" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="L210" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M210" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="19">
+        <v>45745.7333702662</v>
+      </c>
+      <c r="B211" s="20" t="s">
+        <v>540</v>
+      </c>
+      <c r="C211" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="D211" s="20">
+        <v>2.024622E7</v>
+      </c>
+      <c r="E211" s="20" t="s">
+        <v>541</v>
+      </c>
+      <c r="F211" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G211" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H211" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I211" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J211" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K211" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L211" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M211" s="20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="15">
+        <v>45745.76791119213</v>
+      </c>
+      <c r="B212" s="16" t="s">
+        <v>542</v>
+      </c>
+      <c r="C212" s="16" t="s">
+        <v>543</v>
+      </c>
+      <c r="D212" s="16">
+        <v>2.0246737E7</v>
+      </c>
+      <c r="E212" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="F212" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G212" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="H212" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="I212" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="J212" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K212" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="L212" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M212" s="16" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="19">
+        <v>45745.83696878472</v>
+      </c>
+      <c r="B213" s="20" t="s">
+        <v>545</v>
+      </c>
+      <c r="C213" s="20" t="s">
+        <v>546</v>
+      </c>
+      <c r="D213" s="20">
+        <v>2.0243331E7</v>
+      </c>
+      <c r="E213" s="20" t="s">
+        <v>547</v>
+      </c>
+      <c r="F213" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G213" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="H213" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I213" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="J213" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K213" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="L213" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M213" s="20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="15">
+        <v>45745.83874885416</v>
+      </c>
+      <c r="B214" s="16" t="s">
+        <v>548</v>
+      </c>
+      <c r="C214" s="16" t="s">
+        <v>549</v>
+      </c>
+      <c r="D214" s="16">
+        <v>2.023335E7</v>
+      </c>
+      <c r="E214" s="16" t="s">
+        <v>550</v>
+      </c>
+      <c r="F214" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G214" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="H214" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="I214" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J214" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K214" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L214" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N214" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="19">
+        <v>45745.8472565625</v>
+      </c>
+      <c r="B215" s="20" t="s">
+        <v>551</v>
+      </c>
+      <c r="C215" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D215" s="20">
+        <v>2.0223044E7</v>
+      </c>
+      <c r="E215" s="20" t="s">
+        <v>552</v>
+      </c>
+      <c r="F215" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G215" s="21">
+        <v>0.9</v>
+      </c>
+      <c r="H215" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I215" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="J215" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K215" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="L215" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N215" s="22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="15">
+        <v>45745.85711679398</v>
+      </c>
+      <c r="B216" s="16" t="s">
+        <v>553</v>
+      </c>
+      <c r="C216" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="D216" s="16">
+        <v>2.0237008E7</v>
+      </c>
+      <c r="E216" s="16" t="s">
+        <v>554</v>
+      </c>
+      <c r="F216" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G216" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="H216" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="I216" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="J216" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K216" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="L216" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M216" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="19">
+        <v>45745.87063959491</v>
+      </c>
+      <c r="B217" s="20" t="s">
+        <v>555</v>
+      </c>
+      <c r="C217" s="20" t="s">
+        <v>556</v>
+      </c>
+      <c r="D217" s="20">
+        <v>2.0223329E7</v>
+      </c>
+      <c r="E217" s="20" t="s">
+        <v>557</v>
+      </c>
+      <c r="F217" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G217" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H217" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I217" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J217" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K217" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L217" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N217" s="22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="15">
+        <v>45745.870676886574</v>
+      </c>
+      <c r="B218" s="16" t="s">
+        <v>558</v>
+      </c>
+      <c r="C218" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="D218" s="16">
+        <v>2.0223302E7</v>
+      </c>
+      <c r="E218" s="16" t="s">
+        <v>559</v>
+      </c>
+      <c r="F218" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G218" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H218" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I218" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J218" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K218" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L218" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N218" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="19">
+        <v>45745.87069729167</v>
+      </c>
+      <c r="B219" s="20" t="s">
+        <v>560</v>
+      </c>
+      <c r="C219" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="D219" s="20">
+        <v>2.0223331E7</v>
+      </c>
+      <c r="E219" s="20" t="s">
+        <v>561</v>
+      </c>
+      <c r="F219" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G219" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H219" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I219" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J219" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K219" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L219" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M219" s="20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="15">
+        <v>45745.88351251157</v>
+      </c>
+      <c r="B220" s="16" t="s">
+        <v>562</v>
+      </c>
+      <c r="C220" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="D220" s="16">
+        <v>2.0226702E7</v>
+      </c>
+      <c r="E220" s="16" t="s">
+        <v>563</v>
+      </c>
+      <c r="F220" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G220" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H220" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I220" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="J220" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K220" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L220" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M220" s="16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="19">
+        <v>45745.90134802084</v>
+      </c>
+      <c r="B221" s="20" t="s">
+        <v>564</v>
+      </c>
+      <c r="C221" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="D221" s="20">
+        <v>2.0233418E7</v>
+      </c>
+      <c r="E221" s="20" t="s">
+        <v>565</v>
+      </c>
+      <c r="F221" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G221" s="21">
+        <v>0.7</v>
+      </c>
+      <c r="H221" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I221" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J221" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="K221" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L221" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M221" s="20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="15">
+        <v>45745.90158975695</v>
+      </c>
+      <c r="B222" s="16" t="s">
+        <v>566</v>
+      </c>
+      <c r="C222" s="16" t="s">
+        <v>259</v>
+      </c>
+      <c r="D222" s="16">
+        <v>2.0241726E7</v>
+      </c>
+      <c r="E222" s="16" t="s">
+        <v>567</v>
+      </c>
+      <c r="F222" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="G222" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H222" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I222" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J222" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K222" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L222" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N222" s="18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="19">
+        <v>45745.90165545139</v>
+      </c>
+      <c r="B223" s="20" t="s">
+        <v>568</v>
+      </c>
+      <c r="C223" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="D223" s="20">
+        <v>2.0223716E7</v>
+      </c>
+      <c r="E223" s="20" t="s">
+        <v>569</v>
+      </c>
+      <c r="F223" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G223" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="H223" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="I223" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J223" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="K223" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="L223" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M223" s="20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="15">
+        <v>45745.90739273148</v>
+      </c>
+      <c r="B224" s="16" t="s">
+        <v>570</v>
+      </c>
+      <c r="C224" s="16" t="s">
+        <v>571</v>
+      </c>
+      <c r="D224" s="16">
+        <v>2.0246401E7</v>
+      </c>
+      <c r="E224" s="16" t="s">
+        <v>572</v>
+      </c>
+      <c r="F224" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G224" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H224" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I224" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J224" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K224" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L224" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N224" s="18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="19">
+        <v>45745.91702142361</v>
+      </c>
+      <c r="B225" s="20" t="s">
+        <v>573</v>
+      </c>
+      <c r="C225" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="D225" s="20">
+        <v>2.0242744E7</v>
+      </c>
+      <c r="E225" s="20" t="s">
+        <v>574</v>
+      </c>
+      <c r="F225" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G225" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H225" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I225" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J225" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K225" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L225" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M225" s="20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="15">
+        <v>45745.92638228009</v>
+      </c>
+      <c r="B226" s="16" t="s">
+        <v>575</v>
+      </c>
+      <c r="C226" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D226" s="16">
+        <v>2.0222962E7</v>
+      </c>
+      <c r="E226" s="16" t="s">
+        <v>576</v>
+      </c>
+      <c r="F226" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="G226" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="H226" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="I226" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="J226" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="K226" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L226" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M226" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="23">
+        <v>45745.945019861116</v>
+      </c>
+      <c r="B227" s="24" t="s">
+        <v>577</v>
+      </c>
+      <c r="C227" s="24" t="s">
+        <v>578</v>
+      </c>
+      <c r="D227" s="24">
+        <v>2.0241725E7</v>
+      </c>
+      <c r="E227" s="24" t="s">
+        <v>579</v>
+      </c>
+      <c r="F227" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="G227" s="25">
+        <v>0.3</v>
+      </c>
+      <c r="H227" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="I227" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="J227" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="K227" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="L227" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="N227" s="26" t="s">
         <v>22</v>
       </c>
     </row>

--- a/R/data/quiz_250324.xlsx
+++ b/R/data/quiz_250324.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2274" uniqueCount="580">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3214" uniqueCount="775">
   <si>
     <t>타임스탬프</t>
   </si>
@@ -1751,6 +1751,591 @@
   </si>
   <si>
     <t>이현민</t>
+  </si>
+  <si>
+    <t>thd2270@gmail.com</t>
+  </si>
+  <si>
+    <t>강예송</t>
+  </si>
+  <si>
+    <t>kimminsu7063@gmail.com</t>
+  </si>
+  <si>
+    <t>김민수</t>
+  </si>
+  <si>
+    <t>juduse9@naver.com</t>
+  </si>
+  <si>
+    <t>박시은</t>
+  </si>
+  <si>
+    <t>romma37@naver.com</t>
+  </si>
+  <si>
+    <t>이새롬</t>
+  </si>
+  <si>
+    <t>rga0801@naver.com</t>
+  </si>
+  <si>
+    <t>김형민</t>
+  </si>
+  <si>
+    <t>llimjh123@naver.com</t>
+  </si>
+  <si>
+    <t>임준완</t>
+  </si>
+  <si>
+    <t>jenny_0603@naver.com</t>
+  </si>
+  <si>
+    <t>이지수</t>
+  </si>
+  <si>
+    <t>050822ac@gmail.com</t>
+  </si>
+  <si>
+    <t>조연솔</t>
+  </si>
+  <si>
+    <t>chaeeul9122@gmail.com</t>
+  </si>
+  <si>
+    <t>김채을</t>
+  </si>
+  <si>
+    <t>qwe1527@naver.com</t>
+  </si>
+  <si>
+    <t>김나은</t>
+  </si>
+  <si>
+    <t>kwan0172@gmail.com</t>
+  </si>
+  <si>
+    <t>김관형</t>
+  </si>
+  <si>
+    <t>j92921652@gmail.com</t>
+  </si>
+  <si>
+    <t>정주원</t>
+  </si>
+  <si>
+    <t>csb5042@hanmail.net</t>
+  </si>
+  <si>
+    <t>최수빈</t>
+  </si>
+  <si>
+    <t>000727yjh@naver.com</t>
+  </si>
+  <si>
+    <t>윤종현</t>
+  </si>
+  <si>
+    <t>psh19851985@gmail.com</t>
+  </si>
+  <si>
+    <t>박성호</t>
+  </si>
+  <si>
+    <t>quf080411@gmail.com</t>
+  </si>
+  <si>
+    <t>김태연</t>
+  </si>
+  <si>
+    <t>bellita0321@naver.com</t>
+  </si>
+  <si>
+    <t>손가연</t>
+  </si>
+  <si>
+    <t>host051006@gmail.com</t>
+  </si>
+  <si>
+    <t>윤아영</t>
+  </si>
+  <si>
+    <t>zosel1595@naver.com</t>
+  </si>
+  <si>
+    <t>콘텐츠 IT 전공</t>
+  </si>
+  <si>
+    <t>최성민</t>
+  </si>
+  <si>
+    <t>ksyprosch11@gmail.com</t>
+  </si>
+  <si>
+    <t>김서연</t>
+  </si>
+  <si>
+    <t>yangsj0626@gmail.com</t>
+  </si>
+  <si>
+    <t>양선준</t>
+  </si>
+  <si>
+    <t>chayoung1205@gmail.com</t>
+  </si>
+  <si>
+    <t>김찬영</t>
+  </si>
+  <si>
+    <t>justin99961@gmail.com</t>
+  </si>
+  <si>
+    <t>조연서</t>
+  </si>
+  <si>
+    <t>chxxhxxck@naver.com</t>
+  </si>
+  <si>
+    <t>박찬혁</t>
+  </si>
+  <si>
+    <t>boeun050214@naver.com</t>
+  </si>
+  <si>
+    <t>이보은</t>
+  </si>
+  <si>
+    <t>juliaj03@naver.com</t>
+  </si>
+  <si>
+    <t>정한결</t>
+  </si>
+  <si>
+    <t>lcs7714567@naver.com</t>
+  </si>
+  <si>
+    <t>gmltjd050406@gmail.com</t>
+  </si>
+  <si>
+    <t>김희성</t>
+  </si>
+  <si>
+    <t>dustj9033@gmail.com</t>
+  </si>
+  <si>
+    <t>고연서</t>
+  </si>
+  <si>
+    <t>song_050929@naver.com</t>
+  </si>
+  <si>
+    <t>송은채</t>
+  </si>
+  <si>
+    <t>dltmdrb7013@gmail.com</t>
+  </si>
+  <si>
+    <t>이승규</t>
+  </si>
+  <si>
+    <t>jsjhsuper@gmail.com</t>
+  </si>
+  <si>
+    <t>반도체디스플레이어 스쿨</t>
+  </si>
+  <si>
+    <t>kdh000224@naver.com</t>
+  </si>
+  <si>
+    <t>김동현</t>
+  </si>
+  <si>
+    <t>bong8hee@gmail.com</t>
+  </si>
+  <si>
+    <t>강태웅</t>
+  </si>
+  <si>
+    <t>iyw120@naver.com</t>
+  </si>
+  <si>
+    <t>박규빈</t>
+  </si>
+  <si>
+    <t>jooyj03@gmail.com</t>
+  </si>
+  <si>
+    <t>주의진</t>
+  </si>
+  <si>
+    <t>gka4057@naver.com</t>
+  </si>
+  <si>
+    <t>함효린</t>
+  </si>
+  <si>
+    <t>opopkang0528@gmail.com</t>
+  </si>
+  <si>
+    <t>강현지</t>
+  </si>
+  <si>
+    <t>2005jkjk@naver.com</t>
+  </si>
+  <si>
+    <t>최나윤</t>
+  </si>
+  <si>
+    <t>lee.jaehyeok0903@gmail.com</t>
+  </si>
+  <si>
+    <t>이재혁</t>
+  </si>
+  <si>
+    <t>rudtlr419@naver.com</t>
+  </si>
+  <si>
+    <t>장경식</t>
+  </si>
+  <si>
+    <t>seoulsion123@gmail.com</t>
+  </si>
+  <si>
+    <t>최시온</t>
+  </si>
+  <si>
+    <t>leedaeun0409@naver.com</t>
+  </si>
+  <si>
+    <t>이다은</t>
+  </si>
+  <si>
+    <t>woojoong0221@gmail.com</t>
+  </si>
+  <si>
+    <t>김우중</t>
+  </si>
+  <si>
+    <t>echanwoo48@gmail.com</t>
+  </si>
+  <si>
+    <t>이찬우</t>
+  </si>
+  <si>
+    <t>jysjys1006@naver.com</t>
+  </si>
+  <si>
+    <t>지예슬</t>
+  </si>
+  <si>
+    <t>rmsgml52@gmail.com</t>
+  </si>
+  <si>
+    <t>글로벌비즈니스전공</t>
+  </si>
+  <si>
+    <t>장근희</t>
+  </si>
+  <si>
+    <t>lunarena0719@naver.com</t>
+  </si>
+  <si>
+    <t>채은서</t>
+  </si>
+  <si>
+    <t>gksrjs0602@naver.com</t>
+  </si>
+  <si>
+    <t>한건희</t>
+  </si>
+  <si>
+    <t>hwangdaeun09@gmail.com</t>
+  </si>
+  <si>
+    <t>황다은</t>
+  </si>
+  <si>
+    <t>swh12q@gmail.com</t>
+  </si>
+  <si>
+    <t>권지영</t>
+  </si>
+  <si>
+    <t>kimminwoo78901@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">러시아학과 </t>
+  </si>
+  <si>
+    <t>김민우</t>
+  </si>
+  <si>
+    <t>sob3099@gmail.com</t>
+  </si>
+  <si>
+    <t>송종현</t>
+  </si>
+  <si>
+    <t>aannddyy350@gmail.com</t>
+  </si>
+  <si>
+    <t>이승환</t>
+  </si>
+  <si>
+    <t>hansuhyun0809@naver.com</t>
+  </si>
+  <si>
+    <t>한수현</t>
+  </si>
+  <si>
+    <t>dltldms0908@naver.com</t>
+  </si>
+  <si>
+    <t>이시은</t>
+  </si>
+  <si>
+    <t>mikyoung327586@gmail.com</t>
+  </si>
+  <si>
+    <t>박찬희</t>
+  </si>
+  <si>
+    <t>gwkang0330@gmail.com</t>
+  </si>
+  <si>
+    <t>강건우</t>
+  </si>
+  <si>
+    <t>kigkig495@naver.com</t>
+  </si>
+  <si>
+    <t>콘텐츠it</t>
+  </si>
+  <si>
+    <t>오준혁</t>
+  </si>
+  <si>
+    <t>wjdrjs0111@gmail.com</t>
+  </si>
+  <si>
+    <t>정건</t>
+  </si>
+  <si>
+    <t>uksongcheol@naver.com</t>
+  </si>
+  <si>
+    <t>김성철</t>
+  </si>
+  <si>
+    <t>mj09045@naver.com</t>
+  </si>
+  <si>
+    <t>김민재</t>
+  </si>
+  <si>
+    <t>kkimsol@naver.com</t>
+  </si>
+  <si>
+    <t>김솔</t>
+  </si>
+  <si>
+    <t>dagam331@gmail.com</t>
+  </si>
+  <si>
+    <t>명다감</t>
+  </si>
+  <si>
+    <t>lim48664401@gmail.com</t>
+  </si>
+  <si>
+    <t>임동욱</t>
+  </si>
+  <si>
+    <t>hyeri051119@naver.com</t>
+  </si>
+  <si>
+    <t>서혜리</t>
+  </si>
+  <si>
+    <t>nick6723@naver.com</t>
+  </si>
+  <si>
+    <t>미래융합스쿨 의약신소재학과</t>
+  </si>
+  <si>
+    <t>유준상</t>
+  </si>
+  <si>
+    <t>juho0519@naver.com</t>
+  </si>
+  <si>
+    <t>주호연</t>
+  </si>
+  <si>
+    <t>jiwoo1656@naver.com</t>
+  </si>
+  <si>
+    <t>정지우</t>
+  </si>
+  <si>
+    <t>seonwoo6034@naver.com</t>
+  </si>
+  <si>
+    <t>이선우</t>
+  </si>
+  <si>
+    <t>jaho73220@gmail.com</t>
+  </si>
+  <si>
+    <t>이재호</t>
+  </si>
+  <si>
+    <t>rlawlsk0615@naver.com</t>
+  </si>
+  <si>
+    <t>김지나</t>
+  </si>
+  <si>
+    <t>as2020kl@naver.com</t>
+  </si>
+  <si>
+    <t>박수진</t>
+  </si>
+  <si>
+    <t>haenlove1021@naver.com</t>
+  </si>
+  <si>
+    <t>디자인인문예술전공</t>
+  </si>
+  <si>
+    <t>김하은</t>
+  </si>
+  <si>
+    <t>haramie05@naver.com</t>
+  </si>
+  <si>
+    <t>김하람</t>
+  </si>
+  <si>
+    <t>dahan1124man@gmail.com</t>
+  </si>
+  <si>
+    <t>빅데이터 학과</t>
+  </si>
+  <si>
+    <t>장한</t>
+  </si>
+  <si>
+    <t>pio__@naver.com</t>
+  </si>
+  <si>
+    <t>김남영</t>
+  </si>
+  <si>
+    <t>0821choi@gmail.com</t>
+  </si>
+  <si>
+    <t>반도체•디스플레이스쿨</t>
+  </si>
+  <si>
+    <t>hschang0924@gmail.com</t>
+  </si>
+  <si>
+    <t>장현수</t>
+  </si>
+  <si>
+    <t>bluelemon051106@naver.com</t>
+  </si>
+  <si>
+    <t>신정민</t>
+  </si>
+  <si>
+    <t>bestkrh@naver.com</t>
+  </si>
+  <si>
+    <t>김래현</t>
+  </si>
+  <si>
+    <t>20202514@hallym.ac.kr</t>
+  </si>
+  <si>
+    <t>김윤아</t>
+  </si>
+  <si>
+    <t>jun050510@naver.com</t>
+  </si>
+  <si>
+    <t>유한준</t>
+  </si>
+  <si>
+    <t>kmkben@naver.com</t>
+  </si>
+  <si>
+    <t>김민규</t>
+  </si>
+  <si>
+    <t>nody0402@naver.com</t>
+  </si>
+  <si>
+    <t>소프트웨어융합대학 빅데이터 전공</t>
+  </si>
+  <si>
+    <t>박준우</t>
+  </si>
+  <si>
+    <t>seahorse93076714@gmail.com</t>
+  </si>
+  <si>
+    <t>이지원</t>
+  </si>
+  <si>
+    <t>yangkyung04@naver.com</t>
+  </si>
+  <si>
+    <t>양경호</t>
+  </si>
+  <si>
+    <t>h20202591@glab.hallym.ac.kr</t>
+  </si>
+  <si>
+    <t>홍기민</t>
+  </si>
+  <si>
+    <t>gtar7155@gmail.com</t>
+  </si>
+  <si>
+    <t>정민서</t>
+  </si>
+  <si>
+    <t>ayourg@naver.cm</t>
+  </si>
+  <si>
+    <t>신아영</t>
+  </si>
+  <si>
+    <t>namsoy0405@naver.com</t>
+  </si>
+  <si>
+    <t>남소영</t>
+  </si>
+  <si>
+    <t>hb3130@naver.com</t>
+  </si>
+  <si>
+    <t>안효빈</t>
+  </si>
+  <si>
+    <t>20226614@hallym.ac.kr</t>
+  </si>
+  <si>
+    <t>김태현</t>
+  </si>
+  <si>
+    <t>ckdnvd1e@kakao.com</t>
+  </si>
+  <si>
+    <t>이시온</t>
   </si>
 </sst>
 </file>
@@ -2095,7 +2680,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A1:N227" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A1:N321" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="14">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -11609,44 +12194,3898 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="23">
+      <c r="A227" s="19">
         <v>45745.945019861116</v>
       </c>
-      <c r="B227" s="24" t="s">
+      <c r="B227" s="20" t="s">
         <v>577</v>
       </c>
-      <c r="C227" s="24" t="s">
+      <c r="C227" s="20" t="s">
         <v>578</v>
       </c>
-      <c r="D227" s="24">
+      <c r="D227" s="20">
         <v>2.0241725E7</v>
       </c>
-      <c r="E227" s="24" t="s">
+      <c r="E227" s="20" t="s">
         <v>579</v>
       </c>
-      <c r="F227" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="G227" s="25">
+      <c r="F227" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G227" s="21">
         <v>0.3</v>
       </c>
-      <c r="H227" s="24" t="s">
+      <c r="H227" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="I227" s="24" t="s">
+      <c r="I227" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="J227" s="24" t="s">
+      <c r="J227" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="K227" s="24" t="s">
+      <c r="K227" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="L227" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="N227" s="26" t="s">
+      <c r="L227" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N227" s="22" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="15">
+        <v>45745.97097943287</v>
+      </c>
+      <c r="B228" s="16" t="s">
+        <v>580</v>
+      </c>
+      <c r="C228" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D228" s="16">
+        <v>2.0243701E7</v>
+      </c>
+      <c r="E228" s="16" t="s">
+        <v>581</v>
+      </c>
+      <c r="F228" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G228" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H228" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I228" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="J228" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K228" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L228" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M228" s="16" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="19">
+        <v>45746.02142859953</v>
+      </c>
+      <c r="B229" s="20" t="s">
+        <v>582</v>
+      </c>
+      <c r="C229" s="20" t="s">
+        <v>442</v>
+      </c>
+      <c r="D229" s="20">
+        <v>2.0241011E7</v>
+      </c>
+      <c r="E229" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="F229" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G229" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="H229" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="I229" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J229" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K229" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="L229" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M229" s="20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="15">
+        <v>45746.04072902778</v>
+      </c>
+      <c r="B230" s="16" t="s">
+        <v>584</v>
+      </c>
+      <c r="C230" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="D230" s="16">
+        <v>2.0246237E7</v>
+      </c>
+      <c r="E230" s="16" t="s">
+        <v>585</v>
+      </c>
+      <c r="F230" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G230" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H230" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I230" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="J230" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K230" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L230" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M230" s="16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="19">
+        <v>45746.04882125</v>
+      </c>
+      <c r="B231" s="20" t="s">
+        <v>586</v>
+      </c>
+      <c r="C231" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="D231" s="20">
+        <v>2.0243935E7</v>
+      </c>
+      <c r="E231" s="20" t="s">
+        <v>587</v>
+      </c>
+      <c r="F231" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G231" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H231" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I231" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J231" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K231" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L231" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M231" s="20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="15">
+        <v>45746.076762199074</v>
+      </c>
+      <c r="B232" s="16" t="s">
+        <v>588</v>
+      </c>
+      <c r="C232" s="16" t="s">
+        <v>516</v>
+      </c>
+      <c r="D232" s="16">
+        <v>2.0215146E7</v>
+      </c>
+      <c r="E232" s="16" t="s">
+        <v>589</v>
+      </c>
+      <c r="F232" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G232" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H232" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I232" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="J232" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K232" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L232" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M232" s="16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="19">
+        <v>45746.11159158565</v>
+      </c>
+      <c r="B233" s="20" t="s">
+        <v>590</v>
+      </c>
+      <c r="C233" s="20" t="s">
+        <v>221</v>
+      </c>
+      <c r="D233" s="20">
+        <v>2.0225239E7</v>
+      </c>
+      <c r="E233" s="20" t="s">
+        <v>591</v>
+      </c>
+      <c r="F233" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G233" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H233" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I233" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J233" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K233" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="L233" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N233" s="22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="15">
+        <v>45746.11178542824</v>
+      </c>
+      <c r="B234" s="16" t="s">
+        <v>592</v>
+      </c>
+      <c r="C234" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D234" s="16">
+        <v>2.021302E7</v>
+      </c>
+      <c r="E234" s="16" t="s">
+        <v>593</v>
+      </c>
+      <c r="F234" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="G234" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H234" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I234" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J234" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K234" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L234" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N234" s="18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="19">
+        <v>45746.304088414356</v>
+      </c>
+      <c r="B235" s="20" t="s">
+        <v>594</v>
+      </c>
+      <c r="C235" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="D235" s="20">
+        <v>2.0242748E7</v>
+      </c>
+      <c r="E235" s="20" t="s">
+        <v>595</v>
+      </c>
+      <c r="F235" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="G235" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="H235" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="I235" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J235" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K235" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="L235" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M235" s="20" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="15">
+        <v>45746.38335027778</v>
+      </c>
+      <c r="B236" s="16" t="s">
+        <v>596</v>
+      </c>
+      <c r="C236" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="D236" s="16">
+        <v>2.0246228E7</v>
+      </c>
+      <c r="E236" s="16" t="s">
+        <v>597</v>
+      </c>
+      <c r="F236" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="G236" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="H236" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="I236" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="J236" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K236" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L236" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M236" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="19">
+        <v>45746.40809711805</v>
+      </c>
+      <c r="B237" s="20" t="s">
+        <v>598</v>
+      </c>
+      <c r="C237" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="D237" s="20">
+        <v>2.0232504E7</v>
+      </c>
+      <c r="E237" s="20" t="s">
+        <v>599</v>
+      </c>
+      <c r="F237" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G237" s="21">
+        <v>0.7</v>
+      </c>
+      <c r="H237" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="I237" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J237" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="K237" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="L237" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N237" s="22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="15">
+        <v>45746.41310276621</v>
+      </c>
+      <c r="B238" s="16" t="s">
+        <v>600</v>
+      </c>
+      <c r="C238" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D238" s="16">
+        <v>2.021291E7</v>
+      </c>
+      <c r="E238" s="16" t="s">
+        <v>601</v>
+      </c>
+      <c r="F238" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G238" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H238" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="I238" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="J238" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K238" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="L238" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M238" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="19">
+        <v>45746.4191596875</v>
+      </c>
+      <c r="B239" s="20" t="s">
+        <v>602</v>
+      </c>
+      <c r="C239" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="D239" s="20">
+        <v>2.0243952E7</v>
+      </c>
+      <c r="E239" s="20" t="s">
+        <v>603</v>
+      </c>
+      <c r="F239" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G239" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H239" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I239" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J239" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K239" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L239" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N239" s="22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="15">
+        <v>45746.43303966435</v>
+      </c>
+      <c r="B240" s="16" t="s">
+        <v>604</v>
+      </c>
+      <c r="C240" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D240" s="16">
+        <v>2.0242849E7</v>
+      </c>
+      <c r="E240" s="16" t="s">
+        <v>605</v>
+      </c>
+      <c r="F240" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G240" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H240" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I240" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J240" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K240" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L240" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N240" s="18" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="19">
+        <v>45746.43863091435</v>
+      </c>
+      <c r="B241" s="20" t="s">
+        <v>606</v>
+      </c>
+      <c r="C241" s="20" t="s">
+        <v>348</v>
+      </c>
+      <c r="D241" s="20">
+        <v>2.0235218E7</v>
+      </c>
+      <c r="E241" s="20" t="s">
+        <v>607</v>
+      </c>
+      <c r="F241" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G241" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H241" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I241" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J241" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K241" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L241" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N241" s="22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="15">
+        <v>45746.45211157408</v>
+      </c>
+      <c r="B242" s="16" t="s">
+        <v>608</v>
+      </c>
+      <c r="C242" s="16" t="s">
+        <v>348</v>
+      </c>
+      <c r="D242" s="16">
+        <v>2.0215156E7</v>
+      </c>
+      <c r="E242" s="16" t="s">
+        <v>609</v>
+      </c>
+      <c r="F242" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G242" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H242" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I242" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J242" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K242" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L242" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N242" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="19">
+        <v>45746.453590833335</v>
+      </c>
+      <c r="B243" s="20" t="s">
+        <v>610</v>
+      </c>
+      <c r="C243" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="D243" s="20">
+        <v>2.0246229E7</v>
+      </c>
+      <c r="E243" s="20" t="s">
+        <v>611</v>
+      </c>
+      <c r="F243" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G243" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="H243" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="I243" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="J243" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K243" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L243" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M243" s="20" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="15">
+        <v>45746.457900925925</v>
+      </c>
+      <c r="B244" s="16" t="s">
+        <v>612</v>
+      </c>
+      <c r="C244" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D244" s="16">
+        <v>2.023297E7</v>
+      </c>
+      <c r="E244" s="16" t="s">
+        <v>613</v>
+      </c>
+      <c r="F244" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G244" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H244" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I244" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J244" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K244" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L244" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N244" s="18" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="19">
+        <v>45746.4782072338</v>
+      </c>
+      <c r="B245" s="20" t="s">
+        <v>614</v>
+      </c>
+      <c r="C245" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="D245" s="20">
+        <v>2.0246929E7</v>
+      </c>
+      <c r="E245" s="20" t="s">
+        <v>615</v>
+      </c>
+      <c r="F245" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G245" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="H245" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I245" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J245" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="K245" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="L245" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N245" s="22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="15">
+        <v>45746.47858385417</v>
+      </c>
+      <c r="B246" s="16" t="s">
+        <v>616</v>
+      </c>
+      <c r="C246" s="16" t="s">
+        <v>617</v>
+      </c>
+      <c r="D246" s="16">
+        <v>2.022326E7</v>
+      </c>
+      <c r="E246" s="16" t="s">
+        <v>618</v>
+      </c>
+      <c r="F246" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="G246" s="17">
+        <v>0.7</v>
+      </c>
+      <c r="H246" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="I246" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="J246" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="K246" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L246" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M246" s="16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="19">
+        <v>45746.51550818287</v>
+      </c>
+      <c r="B247" s="20" t="s">
+        <v>619</v>
+      </c>
+      <c r="C247" s="20" t="s">
+        <v>450</v>
+      </c>
+      <c r="D247" s="20">
+        <v>2.0245129E7</v>
+      </c>
+      <c r="E247" s="20" t="s">
+        <v>620</v>
+      </c>
+      <c r="F247" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G247" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H247" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I247" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J247" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K247" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L247" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N247" s="22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="15">
+        <v>45746.52632806713</v>
+      </c>
+      <c r="B248" s="16" t="s">
+        <v>621</v>
+      </c>
+      <c r="C248" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="D248" s="16">
+        <v>2.0222222E7</v>
+      </c>
+      <c r="E248" s="16" t="s">
+        <v>622</v>
+      </c>
+      <c r="F248" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="G248" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H248" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I248" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J248" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K248" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L248" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M248" s="16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="19">
+        <v>45746.526586168984</v>
+      </c>
+      <c r="B249" s="20" t="s">
+        <v>623</v>
+      </c>
+      <c r="C249" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="D249" s="20">
+        <v>2.0223512E7</v>
+      </c>
+      <c r="E249" s="20" t="s">
+        <v>624</v>
+      </c>
+      <c r="F249" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G249" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H249" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I249" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="J249" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K249" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L249" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M249" s="20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="15">
+        <v>45746.53071614583</v>
+      </c>
+      <c r="B250" s="16" t="s">
+        <v>625</v>
+      </c>
+      <c r="C250" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="D250" s="16">
+        <v>2.0196285E7</v>
+      </c>
+      <c r="E250" s="16" t="s">
+        <v>626</v>
+      </c>
+      <c r="F250" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G250" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="H250" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I250" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="J250" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K250" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L250" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M250" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="19">
+        <v>45746.535183252316</v>
+      </c>
+      <c r="B251" s="20" t="s">
+        <v>627</v>
+      </c>
+      <c r="C251" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="D251" s="20">
+        <v>2.0202616E7</v>
+      </c>
+      <c r="E251" s="20" t="s">
+        <v>628</v>
+      </c>
+      <c r="F251" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G251" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H251" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I251" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J251" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K251" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L251" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N251" s="22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="15">
+        <v>45746.5361453125</v>
+      </c>
+      <c r="B252" s="16" t="s">
+        <v>629</v>
+      </c>
+      <c r="C252" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="D252" s="16">
+        <v>2.0242546E7</v>
+      </c>
+      <c r="E252" s="16" t="s">
+        <v>630</v>
+      </c>
+      <c r="F252" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G252" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H252" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="I252" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="J252" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K252" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="L252" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N252" s="18" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="19">
+        <v>45746.544588310186</v>
+      </c>
+      <c r="B253" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="C253" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="D253" s="20">
+        <v>2.0243954E7</v>
+      </c>
+      <c r="E253" s="20" t="s">
+        <v>632</v>
+      </c>
+      <c r="F253" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G253" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H253" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I253" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="J253" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K253" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L253" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N253" s="22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="15">
+        <v>45746.55025608796</v>
+      </c>
+      <c r="B254" s="16" t="s">
+        <v>633</v>
+      </c>
+      <c r="C254" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="D254" s="16">
+        <v>2.0227056E7</v>
+      </c>
+      <c r="E254" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="F254" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G254" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="H254" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="I254" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="J254" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K254" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="L254" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N254" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="19">
+        <v>45746.56486586806</v>
+      </c>
+      <c r="B255" s="20" t="s">
+        <v>634</v>
+      </c>
+      <c r="C255" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="D255" s="20">
+        <v>2.0241713E7</v>
+      </c>
+      <c r="E255" s="20" t="s">
+        <v>635</v>
+      </c>
+      <c r="F255" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="G255" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H255" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I255" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="J255" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="K255" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="L255" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N255" s="22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="15">
+        <v>45746.570519155095</v>
+      </c>
+      <c r="B256" s="16" t="s">
+        <v>636</v>
+      </c>
+      <c r="C256" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="D256" s="16">
+        <v>2.0246703E7</v>
+      </c>
+      <c r="E256" s="16" t="s">
+        <v>637</v>
+      </c>
+      <c r="F256" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G256" s="17">
+        <v>0.7</v>
+      </c>
+      <c r="H256" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="I256" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="J256" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K256" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="L256" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N256" s="18" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="19">
+        <v>45746.57225107639</v>
+      </c>
+      <c r="B257" s="20" t="s">
+        <v>638</v>
+      </c>
+      <c r="C257" s="20" t="s">
+        <v>248</v>
+      </c>
+      <c r="D257" s="20">
+        <v>2.0241049E7</v>
+      </c>
+      <c r="E257" s="20" t="s">
+        <v>639</v>
+      </c>
+      <c r="F257" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G257" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H257" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I257" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J257" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K257" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L257" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M257" s="20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="15">
+        <v>45746.58447903935</v>
+      </c>
+      <c r="B258" s="16" t="s">
+        <v>640</v>
+      </c>
+      <c r="C258" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="D258" s="16">
+        <v>2.0251066E7</v>
+      </c>
+      <c r="E258" s="16" t="s">
+        <v>641</v>
+      </c>
+      <c r="F258" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G258" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H258" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="I258" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="J258" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K258" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="L258" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N258" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="19">
+        <v>45746.59257274306</v>
+      </c>
+      <c r="B259" s="20" t="s">
+        <v>642</v>
+      </c>
+      <c r="C259" s="20" t="s">
+        <v>643</v>
+      </c>
+      <c r="D259" s="20">
+        <v>2.0233308E7</v>
+      </c>
+      <c r="E259" s="20" t="s">
+        <v>387</v>
+      </c>
+      <c r="F259" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="G259" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H259" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I259" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="J259" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="K259" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="L259" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N259" s="22" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="15">
+        <v>45746.594062187505</v>
+      </c>
+      <c r="B260" s="16" t="s">
+        <v>644</v>
+      </c>
+      <c r="C260" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D260" s="16">
+        <v>2.0202913E7</v>
+      </c>
+      <c r="E260" s="16" t="s">
+        <v>645</v>
+      </c>
+      <c r="F260" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G260" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H260" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I260" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J260" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K260" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L260" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N260" s="18" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="19">
+        <v>45746.598435023145</v>
+      </c>
+      <c r="B261" s="20" t="s">
+        <v>646</v>
+      </c>
+      <c r="C261" s="20" t="s">
+        <v>274</v>
+      </c>
+      <c r="D261" s="20">
+        <v>2.0202905E7</v>
+      </c>
+      <c r="E261" s="20" t="s">
+        <v>647</v>
+      </c>
+      <c r="F261" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G261" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H261" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I261" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J261" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K261" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L261" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M261" s="20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="15">
+        <v>45746.61204190972</v>
+      </c>
+      <c r="B262" s="16" t="s">
+        <v>648</v>
+      </c>
+      <c r="C262" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D262" s="16">
+        <v>2.0242953E7</v>
+      </c>
+      <c r="E262" s="16" t="s">
+        <v>649</v>
+      </c>
+      <c r="F262" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="G262" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="H262" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I262" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J262" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K262" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L262" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N262" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="19">
+        <v>45746.61655518519</v>
+      </c>
+      <c r="B263" s="20" t="s">
+        <v>650</v>
+      </c>
+      <c r="C263" s="20" t="s">
+        <v>516</v>
+      </c>
+      <c r="D263" s="20">
+        <v>2.0225262E7</v>
+      </c>
+      <c r="E263" s="20" t="s">
+        <v>651</v>
+      </c>
+      <c r="F263" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G263" s="21">
+        <v>0.9</v>
+      </c>
+      <c r="H263" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I263" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J263" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K263" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L263" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N263" s="22" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="15">
+        <v>45746.617479733795</v>
+      </c>
+      <c r="B264" s="16" t="s">
+        <v>652</v>
+      </c>
+      <c r="C264" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="D264" s="16">
+        <v>2.0243848E7</v>
+      </c>
+      <c r="E264" s="16" t="s">
+        <v>653</v>
+      </c>
+      <c r="F264" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G264" s="17">
+        <v>0.7</v>
+      </c>
+      <c r="H264" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="I264" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="J264" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K264" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="L264" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N264" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="19">
+        <v>45746.62398046296</v>
+      </c>
+      <c r="B265" s="20" t="s">
+        <v>654</v>
+      </c>
+      <c r="C265" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="D265" s="20">
+        <v>2.0242203E7</v>
+      </c>
+      <c r="E265" s="20" t="s">
+        <v>655</v>
+      </c>
+      <c r="F265" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G265" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="H265" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="I265" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J265" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K265" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="L265" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M265" s="20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="15">
+        <v>45746.624867569444</v>
+      </c>
+      <c r="B266" s="16" t="s">
+        <v>656</v>
+      </c>
+      <c r="C266" s="16" t="s">
+        <v>571</v>
+      </c>
+      <c r="D266" s="16">
+        <v>2.0246426E7</v>
+      </c>
+      <c r="E266" s="16" t="s">
+        <v>657</v>
+      </c>
+      <c r="F266" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G266" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="H266" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="I266" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="J266" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K266" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="L266" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N266" s="18" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="19">
+        <v>45746.632857916666</v>
+      </c>
+      <c r="B267" s="20" t="s">
+        <v>658</v>
+      </c>
+      <c r="C267" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="D267" s="20">
+        <v>2.024394E7</v>
+      </c>
+      <c r="E267" s="20" t="s">
+        <v>659</v>
+      </c>
+      <c r="F267" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G267" s="21">
+        <v>0.7</v>
+      </c>
+      <c r="H267" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="I267" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J267" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K267" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="L267" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N267" s="22" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="15">
+        <v>45746.63625513889</v>
+      </c>
+      <c r="B268" s="16" t="s">
+        <v>660</v>
+      </c>
+      <c r="C268" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="D268" s="16">
+        <v>2.0242741E7</v>
+      </c>
+      <c r="E268" s="16" t="s">
+        <v>661</v>
+      </c>
+      <c r="F268" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G268" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H268" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="I268" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J268" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K268" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="L268" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M268" s="16" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="19">
+        <v>45746.63684881944</v>
+      </c>
+      <c r="B269" s="20" t="s">
+        <v>662</v>
+      </c>
+      <c r="C269" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="D269" s="20">
+        <v>2.023173E7</v>
+      </c>
+      <c r="E269" s="20" t="s">
+        <v>663</v>
+      </c>
+      <c r="F269" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G269" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="H269" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I269" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J269" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K269" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="L269" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N269" s="22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="15">
+        <v>45746.6395509838</v>
+      </c>
+      <c r="B270" s="16" t="s">
+        <v>664</v>
+      </c>
+      <c r="C270" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="D270" s="16">
+        <v>2.0246263E7</v>
+      </c>
+      <c r="E270" s="16" t="s">
+        <v>665</v>
+      </c>
+      <c r="F270" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G270" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H270" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I270" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J270" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K270" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L270" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M270" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="19">
+        <v>45746.64014658565</v>
+      </c>
+      <c r="B271" s="20" t="s">
+        <v>666</v>
+      </c>
+      <c r="C271" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="D271" s="20">
+        <v>2.0246617E7</v>
+      </c>
+      <c r="E271" s="20" t="s">
+        <v>667</v>
+      </c>
+      <c r="F271" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G271" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H271" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I271" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J271" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K271" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L271" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M271" s="20" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="15">
+        <v>45746.6401899537</v>
+      </c>
+      <c r="B272" s="16" t="s">
+        <v>668</v>
+      </c>
+      <c r="C272" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="D272" s="16">
+        <v>2.0224134E7</v>
+      </c>
+      <c r="E272" s="16" t="s">
+        <v>669</v>
+      </c>
+      <c r="F272" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G272" s="17">
+        <v>0.9</v>
+      </c>
+      <c r="H272" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="I272" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="J272" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K272" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L272" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N272" s="18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="19">
+        <v>45746.641294375004</v>
+      </c>
+      <c r="B273" s="20" t="s">
+        <v>670</v>
+      </c>
+      <c r="C273" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="D273" s="20">
+        <v>2.0217073E7</v>
+      </c>
+      <c r="E273" s="20" t="s">
+        <v>671</v>
+      </c>
+      <c r="F273" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="G273" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H273" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I273" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="J273" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K273" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="L273" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N273" s="22" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="15">
+        <v>45746.643121180554</v>
+      </c>
+      <c r="B274" s="16" t="s">
+        <v>672</v>
+      </c>
+      <c r="C274" s="16" t="s">
+        <v>673</v>
+      </c>
+      <c r="D274" s="16">
+        <v>2.0246417E7</v>
+      </c>
+      <c r="E274" s="16" t="s">
+        <v>674</v>
+      </c>
+      <c r="F274" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G274" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="H274" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="I274" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="J274" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K274" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L274" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M274" s="16" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="19">
+        <v>45746.665555405096</v>
+      </c>
+      <c r="B275" s="20" t="s">
+        <v>675</v>
+      </c>
+      <c r="C275" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="D275" s="20">
+        <v>2.024354E7</v>
+      </c>
+      <c r="E275" s="20" t="s">
+        <v>676</v>
+      </c>
+      <c r="F275" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G275" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H275" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I275" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J275" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K275" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L275" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N275" s="22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="15">
+        <v>45746.66574077547</v>
+      </c>
+      <c r="B276" s="16" t="s">
+        <v>677</v>
+      </c>
+      <c r="C276" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="D276" s="16">
+        <v>2.0242755E7</v>
+      </c>
+      <c r="E276" s="16" t="s">
+        <v>678</v>
+      </c>
+      <c r="F276" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G276" s="17">
+        <v>0.7</v>
+      </c>
+      <c r="H276" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="I276" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="J276" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K276" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="L276" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M276" s="16" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="19">
+        <v>45746.67046637731</v>
+      </c>
+      <c r="B277" s="20" t="s">
+        <v>679</v>
+      </c>
+      <c r="C277" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="D277" s="20">
+        <v>2.025384E7</v>
+      </c>
+      <c r="E277" s="20" t="s">
+        <v>680</v>
+      </c>
+      <c r="F277" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G277" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="H277" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="I277" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J277" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K277" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L277" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M277" s="20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="15">
+        <v>45746.68227232639</v>
+      </c>
+      <c r="B278" s="16" t="s">
+        <v>681</v>
+      </c>
+      <c r="C278" s="16" t="s">
+        <v>511</v>
+      </c>
+      <c r="D278" s="16">
+        <v>2.0246403E7</v>
+      </c>
+      <c r="E278" s="16" t="s">
+        <v>682</v>
+      </c>
+      <c r="F278" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G278" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H278" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="I278" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="J278" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K278" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="L278" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N278" s="18" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="19">
+        <v>45746.69778325231</v>
+      </c>
+      <c r="B279" s="20" t="s">
+        <v>683</v>
+      </c>
+      <c r="C279" s="20" t="s">
+        <v>684</v>
+      </c>
+      <c r="D279" s="20">
+        <v>2.0191702E7</v>
+      </c>
+      <c r="E279" s="20" t="s">
+        <v>685</v>
+      </c>
+      <c r="F279" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G279" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H279" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I279" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J279" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K279" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L279" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M279" s="20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="15">
+        <v>45746.699139317134</v>
+      </c>
+      <c r="B280" s="16" t="s">
+        <v>686</v>
+      </c>
+      <c r="C280" s="16" t="s">
+        <v>248</v>
+      </c>
+      <c r="D280" s="16">
+        <v>2.0231049E7</v>
+      </c>
+      <c r="E280" s="16" t="s">
+        <v>687</v>
+      </c>
+      <c r="F280" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G280" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="H280" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="I280" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="J280" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K280" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L280" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M280" s="16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="19">
+        <v>45746.70058371528</v>
+      </c>
+      <c r="B281" s="20" t="s">
+        <v>688</v>
+      </c>
+      <c r="C281" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D281" s="20">
+        <v>2.0223004E7</v>
+      </c>
+      <c r="E281" s="20" t="s">
+        <v>689</v>
+      </c>
+      <c r="F281" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G281" s="21">
+        <v>0.7</v>
+      </c>
+      <c r="H281" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="I281" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J281" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K281" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="L281" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M281" s="20" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="15">
+        <v>45746.70389640046</v>
+      </c>
+      <c r="B282" s="16" t="s">
+        <v>690</v>
+      </c>
+      <c r="C282" s="16" t="s">
+        <v>248</v>
+      </c>
+      <c r="D282" s="16">
+        <v>2.0241109E7</v>
+      </c>
+      <c r="E282" s="16" t="s">
+        <v>691</v>
+      </c>
+      <c r="F282" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G282" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="H282" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="I282" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="J282" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K282" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="L282" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M282" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="19">
+        <v>45746.70596206019</v>
+      </c>
+      <c r="B283" s="20" t="s">
+        <v>692</v>
+      </c>
+      <c r="C283" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="D283" s="20">
+        <v>2.0231068E7</v>
+      </c>
+      <c r="E283" s="20" t="s">
+        <v>693</v>
+      </c>
+      <c r="F283" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G283" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="H283" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="I283" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J283" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K283" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="L283" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N283" s="22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="15">
+        <v>45746.71561896991</v>
+      </c>
+      <c r="B284" s="16" t="s">
+        <v>694</v>
+      </c>
+      <c r="C284" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="D284" s="16">
+        <v>2.0242523E7</v>
+      </c>
+      <c r="E284" s="16" t="s">
+        <v>695</v>
+      </c>
+      <c r="F284" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G284" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H284" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I284" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J284" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K284" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L284" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M284" s="16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="19">
+        <v>45746.716224062504</v>
+      </c>
+      <c r="B285" s="20" t="s">
+        <v>696</v>
+      </c>
+      <c r="C285" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="D285" s="20">
+        <v>2.0235101E7</v>
+      </c>
+      <c r="E285" s="20" t="s">
+        <v>697</v>
+      </c>
+      <c r="F285" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G285" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="H285" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I285" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="J285" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K285" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="L285" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N285" s="22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="15">
+        <v>45746.72626121528</v>
+      </c>
+      <c r="B286" s="16" t="s">
+        <v>698</v>
+      </c>
+      <c r="C286" s="16" t="s">
+        <v>699</v>
+      </c>
+      <c r="D286" s="16">
+        <v>2.0245205E7</v>
+      </c>
+      <c r="E286" s="16" t="s">
+        <v>700</v>
+      </c>
+      <c r="F286" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="G286" s="17">
+        <v>0.9</v>
+      </c>
+      <c r="H286" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="I286" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="J286" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K286" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="L286" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M286" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="19">
+        <v>45746.73037476852</v>
+      </c>
+      <c r="B287" s="20" t="s">
+        <v>701</v>
+      </c>
+      <c r="C287" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="D287" s="20">
+        <v>2.0244142E7</v>
+      </c>
+      <c r="E287" s="20" t="s">
+        <v>702</v>
+      </c>
+      <c r="F287" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="G287" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H287" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I287" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J287" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K287" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="L287" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M287" s="20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="15">
+        <v>45746.730421238426</v>
+      </c>
+      <c r="B288" s="16" t="s">
+        <v>703</v>
+      </c>
+      <c r="C288" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="D288" s="16">
+        <v>2.0192204E7</v>
+      </c>
+      <c r="E288" s="16" t="s">
+        <v>704</v>
+      </c>
+      <c r="F288" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="G288" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H288" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="I288" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J288" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="K288" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="L288" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M288" s="16" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="19">
+        <v>45746.73160638889</v>
+      </c>
+      <c r="B289" s="20" t="s">
+        <v>705</v>
+      </c>
+      <c r="C289" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D289" s="20">
+        <v>2.0202917E7</v>
+      </c>
+      <c r="E289" s="20" t="s">
+        <v>706</v>
+      </c>
+      <c r="F289" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G289" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="H289" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="I289" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J289" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="K289" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="L289" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N289" s="22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="15">
+        <v>45746.737558125</v>
+      </c>
+      <c r="B290" s="16" t="s">
+        <v>707</v>
+      </c>
+      <c r="C290" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D290" s="16">
+        <v>2.0241514E7</v>
+      </c>
+      <c r="E290" s="16" t="s">
+        <v>708</v>
+      </c>
+      <c r="F290" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="G290" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="H290" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="I290" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J290" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K290" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="L290" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N290" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="19">
+        <v>45746.75278228009</v>
+      </c>
+      <c r="B291" s="20" t="s">
+        <v>709</v>
+      </c>
+      <c r="C291" s="20" t="s">
+        <v>221</v>
+      </c>
+      <c r="D291" s="20">
+        <v>2.0226733E7</v>
+      </c>
+      <c r="E291" s="20" t="s">
+        <v>710</v>
+      </c>
+      <c r="F291" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G291" s="21">
+        <v>0.7</v>
+      </c>
+      <c r="H291" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="I291" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="J291" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K291" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="L291" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M291" s="20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="15">
+        <v>45746.75380186342</v>
+      </c>
+      <c r="B292" s="16" t="s">
+        <v>711</v>
+      </c>
+      <c r="C292" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="D292" s="16">
+        <v>2.0242566E7</v>
+      </c>
+      <c r="E292" s="16" t="s">
+        <v>712</v>
+      </c>
+      <c r="F292" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="G292" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="H292" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="I292" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="J292" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K292" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L292" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M292" s="16" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="19">
+        <v>45746.75393475694</v>
+      </c>
+      <c r="B293" s="20" t="s">
+        <v>713</v>
+      </c>
+      <c r="C293" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="D293" s="20">
+        <v>2.0243515E7</v>
+      </c>
+      <c r="E293" s="20" t="s">
+        <v>714</v>
+      </c>
+      <c r="F293" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="G293" s="21">
+        <v>0.7</v>
+      </c>
+      <c r="H293" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="I293" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J293" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K293" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="L293" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M293" s="20" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="15">
+        <v>45746.755464131944</v>
+      </c>
+      <c r="B294" s="16" t="s">
+        <v>715</v>
+      </c>
+      <c r="C294" s="16" t="s">
+        <v>716</v>
+      </c>
+      <c r="D294" s="16">
+        <v>2.0216626E7</v>
+      </c>
+      <c r="E294" s="16" t="s">
+        <v>717</v>
+      </c>
+      <c r="F294" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G294" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H294" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I294" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="J294" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K294" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L294" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N294" s="18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="19">
+        <v>45746.756000821755</v>
+      </c>
+      <c r="B295" s="20" t="s">
+        <v>718</v>
+      </c>
+      <c r="C295" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D295" s="20">
+        <v>2.0243039E7</v>
+      </c>
+      <c r="E295" s="20" t="s">
+        <v>719</v>
+      </c>
+      <c r="F295" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G295" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="H295" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="I295" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="J295" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K295" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L295" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N295" s="22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="15">
+        <v>45746.759642881945</v>
+      </c>
+      <c r="B296" s="16" t="s">
+        <v>720</v>
+      </c>
+      <c r="C296" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="D296" s="16">
+        <v>2.0232135E7</v>
+      </c>
+      <c r="E296" s="16" t="s">
+        <v>721</v>
+      </c>
+      <c r="F296" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G296" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="H296" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="I296" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="J296" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K296" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="L296" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N296" s="18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="19">
+        <v>45746.76318430556</v>
+      </c>
+      <c r="B297" s="20" t="s">
+        <v>722</v>
+      </c>
+      <c r="C297" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="D297" s="20">
+        <v>2.0244133E7</v>
+      </c>
+      <c r="E297" s="20" t="s">
+        <v>723</v>
+      </c>
+      <c r="F297" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G297" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H297" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I297" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J297" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K297" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L297" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M297" s="20" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="15">
+        <v>45746.7755866088</v>
+      </c>
+      <c r="B298" s="16" t="s">
+        <v>724</v>
+      </c>
+      <c r="C298" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D298" s="16">
+        <v>2.0221532E7</v>
+      </c>
+      <c r="E298" s="16" t="s">
+        <v>725</v>
+      </c>
+      <c r="F298" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G298" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H298" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I298" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J298" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K298" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L298" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N298" s="18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="19">
+        <v>45746.77724509259</v>
+      </c>
+      <c r="B299" s="20" t="s">
+        <v>726</v>
+      </c>
+      <c r="C299" s="20" t="s">
+        <v>248</v>
+      </c>
+      <c r="D299" s="20">
+        <v>2.0221021E7</v>
+      </c>
+      <c r="E299" s="20" t="s">
+        <v>727</v>
+      </c>
+      <c r="F299" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G299" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H299" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I299" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J299" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K299" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L299" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N299" s="22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="15">
+        <v>45746.78952967592</v>
+      </c>
+      <c r="B300" s="16" t="s">
+        <v>728</v>
+      </c>
+      <c r="C300" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D300" s="16">
+        <v>2.0212952E7</v>
+      </c>
+      <c r="E300" s="16" t="s">
+        <v>729</v>
+      </c>
+      <c r="F300" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G300" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="H300" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="I300" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J300" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K300" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L300" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M300" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="19">
+        <v>45746.79913002315</v>
+      </c>
+      <c r="B301" s="20" t="s">
+        <v>730</v>
+      </c>
+      <c r="C301" s="20" t="s">
+        <v>731</v>
+      </c>
+      <c r="D301" s="20">
+        <v>2.024662E7</v>
+      </c>
+      <c r="E301" s="20" t="s">
+        <v>732</v>
+      </c>
+      <c r="F301" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G301" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H301" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I301" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="J301" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K301" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="L301" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N301" s="22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="15">
+        <v>45746.8051709838</v>
+      </c>
+      <c r="B302" s="16" t="s">
+        <v>733</v>
+      </c>
+      <c r="C302" s="16" t="s">
+        <v>313</v>
+      </c>
+      <c r="D302" s="16">
+        <v>2.0242519E7</v>
+      </c>
+      <c r="E302" s="16" t="s">
+        <v>734</v>
+      </c>
+      <c r="F302" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G302" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="H302" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="I302" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J302" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="K302" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="L302" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N302" s="18" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="19">
+        <v>45746.81486951389</v>
+      </c>
+      <c r="B303" s="20" t="s">
+        <v>735</v>
+      </c>
+      <c r="C303" s="20" t="s">
+        <v>736</v>
+      </c>
+      <c r="D303" s="20">
+        <v>2.0225245E7</v>
+      </c>
+      <c r="E303" s="20" t="s">
+        <v>737</v>
+      </c>
+      <c r="F303" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G303" s="21">
+        <v>0.7</v>
+      </c>
+      <c r="H303" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="I303" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="J303" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K303" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="L303" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M303" s="20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="15">
+        <v>45746.81578521991</v>
+      </c>
+      <c r="B304" s="16" t="s">
+        <v>738</v>
+      </c>
+      <c r="C304" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="D304" s="16">
+        <v>2.0227145E7</v>
+      </c>
+      <c r="E304" s="16" t="s">
+        <v>739</v>
+      </c>
+      <c r="F304" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G304" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H304" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I304" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J304" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K304" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L304" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N304" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="19">
+        <v>45746.82301047454</v>
+      </c>
+      <c r="B305" s="20" t="s">
+        <v>740</v>
+      </c>
+      <c r="C305" s="20" t="s">
+        <v>741</v>
+      </c>
+      <c r="D305" s="20">
+        <v>2.0243364E7</v>
+      </c>
+      <c r="E305" s="20" t="s">
+        <v>663</v>
+      </c>
+      <c r="F305" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G305" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H305" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I305" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="J305" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K305" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L305" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N305" s="22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="15">
+        <v>45746.829133761574</v>
+      </c>
+      <c r="B306" s="16" t="s">
+        <v>742</v>
+      </c>
+      <c r="C306" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="D306" s="16">
+        <v>2.0242431E7</v>
+      </c>
+      <c r="E306" s="16" t="s">
+        <v>743</v>
+      </c>
+      <c r="F306" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G306" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="H306" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="I306" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="J306" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="K306" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L306" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M306" s="16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="19">
+        <v>45746.83999278935</v>
+      </c>
+      <c r="B307" s="20" t="s">
+        <v>744</v>
+      </c>
+      <c r="C307" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="D307" s="20">
+        <v>2.0222615E7</v>
+      </c>
+      <c r="E307" s="20" t="s">
+        <v>745</v>
+      </c>
+      <c r="F307" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G307" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="H307" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I307" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J307" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K307" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="L307" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M307" s="20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="15">
+        <v>45746.843861319445</v>
+      </c>
+      <c r="B308" s="16" t="s">
+        <v>746</v>
+      </c>
+      <c r="C308" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D308" s="16">
+        <v>2.0252916E7</v>
+      </c>
+      <c r="E308" s="16" t="s">
+        <v>747</v>
+      </c>
+      <c r="F308" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G308" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H308" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="I308" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J308" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K308" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L308" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N308" s="18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="19">
+        <v>45746.84774182871</v>
+      </c>
+      <c r="B309" s="20" t="s">
+        <v>748</v>
+      </c>
+      <c r="C309" s="20" t="s">
+        <v>371</v>
+      </c>
+      <c r="D309" s="20">
+        <v>2.0202514E7</v>
+      </c>
+      <c r="E309" s="20" t="s">
+        <v>749</v>
+      </c>
+      <c r="F309" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G309" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H309" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I309" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J309" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K309" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="L309" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M309" s="20" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="15">
+        <v>45746.85123648148</v>
+      </c>
+      <c r="B310" s="16" t="s">
+        <v>750</v>
+      </c>
+      <c r="C310" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D310" s="16">
+        <v>2.0241528E7</v>
+      </c>
+      <c r="E310" s="16" t="s">
+        <v>751</v>
+      </c>
+      <c r="F310" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G310" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="H310" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I310" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J310" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K310" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="L310" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M310" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="19">
+        <v>45746.85802730324</v>
+      </c>
+      <c r="B311" s="20" t="s">
+        <v>752</v>
+      </c>
+      <c r="C311" s="20" t="s">
+        <v>516</v>
+      </c>
+      <c r="D311" s="20">
+        <v>2.020513E7</v>
+      </c>
+      <c r="E311" s="20" t="s">
+        <v>753</v>
+      </c>
+      <c r="F311" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G311" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="H311" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I311" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J311" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K311" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="L311" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M311" s="20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="15">
+        <v>45746.85910657408</v>
+      </c>
+      <c r="B312" s="16" t="s">
+        <v>754</v>
+      </c>
+      <c r="C312" s="16" t="s">
+        <v>755</v>
+      </c>
+      <c r="D312" s="16">
+        <v>2.0225163E7</v>
+      </c>
+      <c r="E312" s="16" t="s">
+        <v>756</v>
+      </c>
+      <c r="F312" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G312" s="17">
+        <v>0.9</v>
+      </c>
+      <c r="H312" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="I312" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J312" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K312" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="L312" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N312" s="18" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="19">
+        <v>45746.86255293981</v>
+      </c>
+      <c r="B313" s="20" t="s">
+        <v>757</v>
+      </c>
+      <c r="C313" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="D313" s="20">
+        <v>2.0241229E7</v>
+      </c>
+      <c r="E313" s="20" t="s">
+        <v>758</v>
+      </c>
+      <c r="F313" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="G313" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H313" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I313" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J313" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K313" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="L313" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M313" s="20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="15">
+        <v>45746.866554629625</v>
+      </c>
+      <c r="B314" s="16" t="s">
+        <v>759</v>
+      </c>
+      <c r="C314" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D314" s="16">
+        <v>2.024372E7</v>
+      </c>
+      <c r="E314" s="16" t="s">
+        <v>760</v>
+      </c>
+      <c r="F314" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G314" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H314" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I314" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J314" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K314" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L314" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M314" s="16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="19">
+        <v>45746.87010384259</v>
+      </c>
+      <c r="B315" s="20" t="s">
+        <v>761</v>
+      </c>
+      <c r="C315" s="20" t="s">
+        <v>313</v>
+      </c>
+      <c r="D315" s="20">
+        <v>2.0202591E7</v>
+      </c>
+      <c r="E315" s="20" t="s">
+        <v>762</v>
+      </c>
+      <c r="F315" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G315" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H315" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I315" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J315" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K315" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L315" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N315" s="22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="15">
+        <v>45746.87507317129</v>
+      </c>
+      <c r="B316" s="16" t="s">
+        <v>763</v>
+      </c>
+      <c r="C316" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="D316" s="16">
+        <v>2.0256637E7</v>
+      </c>
+      <c r="E316" s="16" t="s">
+        <v>764</v>
+      </c>
+      <c r="F316" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G316" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H316" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I316" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J316" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K316" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L316" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N316" s="18" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="19">
+        <v>45746.89108422454</v>
+      </c>
+      <c r="B317" s="20" t="s">
+        <v>765</v>
+      </c>
+      <c r="C317" s="20" t="s">
+        <v>336</v>
+      </c>
+      <c r="D317" s="20">
+        <v>2.0242329E7</v>
+      </c>
+      <c r="E317" s="20" t="s">
+        <v>766</v>
+      </c>
+      <c r="F317" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G317" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="H317" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I317" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="J317" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K317" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="L317" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M317" s="20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="15">
+        <v>45746.901937118055</v>
+      </c>
+      <c r="B318" s="16" t="s">
+        <v>767</v>
+      </c>
+      <c r="C318" s="16" t="s">
+        <v>511</v>
+      </c>
+      <c r="D318" s="16">
+        <v>2.0226409E7</v>
+      </c>
+      <c r="E318" s="16" t="s">
+        <v>768</v>
+      </c>
+      <c r="F318" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G318" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H318" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="I318" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="J318" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K318" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="L318" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N318" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="19">
+        <v>45746.903836261576</v>
+      </c>
+      <c r="B319" s="20" t="s">
+        <v>769</v>
+      </c>
+      <c r="C319" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="D319" s="20">
+        <v>2.0241216E7</v>
+      </c>
+      <c r="E319" s="20" t="s">
+        <v>770</v>
+      </c>
+      <c r="F319" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G319" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="H319" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="I319" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J319" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K319" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L319" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M319" s="20" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="15">
+        <v>45746.90633878473</v>
+      </c>
+      <c r="B320" s="16" t="s">
+        <v>771</v>
+      </c>
+      <c r="C320" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="D320" s="16">
+        <v>2.0226614E7</v>
+      </c>
+      <c r="E320" s="16" t="s">
+        <v>772</v>
+      </c>
+      <c r="F320" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G320" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H320" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I320" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J320" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K320" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="L320" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M320" s="16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="23">
+        <v>45746.908776909724</v>
+      </c>
+      <c r="B321" s="24" t="s">
+        <v>773</v>
+      </c>
+      <c r="C321" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="D321" s="24">
+        <v>2.0212744E7</v>
+      </c>
+      <c r="E321" s="24" t="s">
+        <v>774</v>
+      </c>
+      <c r="F321" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="G321" s="25">
+        <v>0.3</v>
+      </c>
+      <c r="H321" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="I321" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="J321" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="K321" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="L321" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="N321" s="26" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/R/data/quiz_250324.xlsx
+++ b/R/data/quiz_250324.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3214" uniqueCount="775">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3254" uniqueCount="783">
   <si>
     <t>타임스탬프</t>
   </si>
@@ -2336,6 +2336,30 @@
   </si>
   <si>
     <t>이시온</t>
+  </si>
+  <si>
+    <t>ssuwan5@gmail.com</t>
+  </si>
+  <si>
+    <t>신수완</t>
+  </si>
+  <si>
+    <t>naebae@naver.com</t>
+  </si>
+  <si>
+    <t>pwtljh123@gmail.com</t>
+  </si>
+  <si>
+    <t>이건정</t>
+  </si>
+  <si>
+    <t>haeyoon205@gmail.com</t>
+  </si>
+  <si>
+    <t>철학전공</t>
+  </si>
+  <si>
+    <t>정해윤</t>
   </si>
 </sst>
 </file>
@@ -2680,7 +2704,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A1:N321" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A1:N325" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="14">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -16048,44 +16072,208 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="23">
+      <c r="A321" s="19">
         <v>45746.908776909724</v>
       </c>
-      <c r="B321" s="24" t="s">
+      <c r="B321" s="20" t="s">
         <v>773</v>
       </c>
-      <c r="C321" s="24" t="s">
+      <c r="C321" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="D321" s="24">
+      <c r="D321" s="20">
         <v>2.0212744E7</v>
       </c>
-      <c r="E321" s="24" t="s">
+      <c r="E321" s="20" t="s">
         <v>774</v>
       </c>
-      <c r="F321" s="24" t="s">
+      <c r="F321" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="G321" s="25">
+      <c r="G321" s="21">
         <v>0.3</v>
       </c>
-      <c r="H321" s="24" t="s">
+      <c r="H321" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="I321" s="24" t="s">
+      <c r="I321" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="J321" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="K321" s="24" t="s">
+      <c r="J321" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K321" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="L321" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="N321" s="26" t="s">
+      <c r="L321" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N321" s="22" t="s">
         <v>31</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="15">
+        <v>45746.940925937495</v>
+      </c>
+      <c r="B322" s="16" t="s">
+        <v>775</v>
+      </c>
+      <c r="C322" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="D322" s="16">
+        <v>2.0202537E7</v>
+      </c>
+      <c r="E322" s="16" t="s">
+        <v>776</v>
+      </c>
+      <c r="F322" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G322" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="H322" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="I322" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J322" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K322" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L322" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N322" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="19">
+        <v>45746.955639444444</v>
+      </c>
+      <c r="B323" s="20" t="s">
+        <v>777</v>
+      </c>
+      <c r="C323" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="D323" s="20">
+        <v>2.0232425E7</v>
+      </c>
+      <c r="E323" s="20" t="s">
+        <v>665</v>
+      </c>
+      <c r="F323" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G323" s="21">
+        <v>0.7</v>
+      </c>
+      <c r="H323" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="I323" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="J323" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K323" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="L323" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N323" s="22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="15">
+        <v>45746.96263685185</v>
+      </c>
+      <c r="B324" s="16" t="s">
+        <v>778</v>
+      </c>
+      <c r="C324" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D324" s="16">
+        <v>2.0222992E7</v>
+      </c>
+      <c r="E324" s="16" t="s">
+        <v>779</v>
+      </c>
+      <c r="F324" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="G324" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H324" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="I324" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="J324" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="K324" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="L324" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M324" s="16" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="23">
+        <v>45746.99255061343</v>
+      </c>
+      <c r="B325" s="24" t="s">
+        <v>780</v>
+      </c>
+      <c r="C325" s="24" t="s">
+        <v>781</v>
+      </c>
+      <c r="D325" s="24">
+        <v>2.0241093E7</v>
+      </c>
+      <c r="E325" s="24" t="s">
+        <v>782</v>
+      </c>
+      <c r="F325" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="G325" s="25">
+        <v>0.3</v>
+      </c>
+      <c r="H325" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="I325" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="J325" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="K325" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="L325" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="N325" s="26" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/R/data/quiz_250324.xlsx
+++ b/R/data/quiz_250324.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3254" uniqueCount="783">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3364" uniqueCount="807">
   <si>
     <t>타임스탬프</t>
   </si>
@@ -2360,6 +2360,78 @@
   </si>
   <si>
     <t>정해윤</t>
+  </si>
+  <si>
+    <t>wookyung7536@naver.com</t>
+  </si>
+  <si>
+    <t>양우경</t>
+  </si>
+  <si>
+    <t>sinsujin0121@gmail.com</t>
+  </si>
+  <si>
+    <t>신수진</t>
+  </si>
+  <si>
+    <t>skgurwls0416@gmail.com</t>
+  </si>
+  <si>
+    <t>나혁진</t>
+  </si>
+  <si>
+    <t>pyo9630@gmail.com</t>
+  </si>
+  <si>
+    <t>이충영</t>
+  </si>
+  <si>
+    <t>ehclfjqm@naver.com</t>
+  </si>
+  <si>
+    <t>변수현</t>
+  </si>
+  <si>
+    <t>kimfoxmj@gmail.com</t>
+  </si>
+  <si>
+    <t>김민지</t>
+  </si>
+  <si>
+    <t>tjdbs_s@naver.com</t>
+  </si>
+  <si>
+    <t>의약신소재전공</t>
+  </si>
+  <si>
+    <t>최서윤</t>
+  </si>
+  <si>
+    <t>ychoe119@gmail.com</t>
+  </si>
+  <si>
+    <t>최윤서</t>
+  </si>
+  <si>
+    <t>djfvks@naver.com</t>
+  </si>
+  <si>
+    <t>이승주</t>
+  </si>
+  <si>
+    <t>qmpzalwn@naver.com</t>
+  </si>
+  <si>
+    <t>글로벌비즈니스 전공</t>
+  </si>
+  <si>
+    <t>오유택</t>
+  </si>
+  <si>
+    <t>juheepoiu@gmail.com</t>
+  </si>
+  <si>
+    <t>임주희</t>
   </si>
 </sst>
 </file>
@@ -2523,10 +2595,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -2534,13 +2606,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -2548,13 +2620,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </left>
       <right style="thin">
         <color rgb="FF442F65"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -2704,7 +2776,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A1:N325" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A1:N336" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="14">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -16236,44 +16308,495 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="23">
+      <c r="A325" s="19">
         <v>45746.99255061343</v>
       </c>
-      <c r="B325" s="24" t="s">
+      <c r="B325" s="20" t="s">
         <v>780</v>
       </c>
-      <c r="C325" s="24" t="s">
+      <c r="C325" s="20" t="s">
         <v>781</v>
       </c>
-      <c r="D325" s="24">
+      <c r="D325" s="20">
         <v>2.0241093E7</v>
       </c>
-      <c r="E325" s="24" t="s">
+      <c r="E325" s="20" t="s">
         <v>782</v>
       </c>
-      <c r="F325" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="G325" s="25">
+      <c r="F325" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G325" s="21">
         <v>0.3</v>
       </c>
-      <c r="H325" s="24" t="s">
+      <c r="H325" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="I325" s="24" t="s">
+      <c r="I325" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="J325" s="24" t="s">
+      <c r="J325" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="K325" s="24" t="s">
+      <c r="K325" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="L325" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="N325" s="26" t="s">
+      <c r="L325" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N325" s="22" t="s">
         <v>94</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="15">
+        <v>45747.03870525463</v>
+      </c>
+      <c r="B326" s="16" t="s">
+        <v>783</v>
+      </c>
+      <c r="C326" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="D326" s="16">
+        <v>2.0212223E7</v>
+      </c>
+      <c r="E326" s="16" t="s">
+        <v>784</v>
+      </c>
+      <c r="F326" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G326" s="17">
+        <v>0.9</v>
+      </c>
+      <c r="H326" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="I326" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="J326" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K326" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="L326" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M326" s="16" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="19">
+        <v>45747.384127557874</v>
+      </c>
+      <c r="B327" s="20" t="s">
+        <v>785</v>
+      </c>
+      <c r="C327" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="D327" s="20">
+        <v>2.0242622E7</v>
+      </c>
+      <c r="E327" s="20" t="s">
+        <v>786</v>
+      </c>
+      <c r="F327" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G327" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H327" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I327" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="J327" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K327" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="L327" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N327" s="22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="15">
+        <v>45747.40961478009</v>
+      </c>
+      <c r="B328" s="16" t="s">
+        <v>787</v>
+      </c>
+      <c r="C328" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="D328" s="16">
+        <v>2.0242716E7</v>
+      </c>
+      <c r="E328" s="16" t="s">
+        <v>788</v>
+      </c>
+      <c r="F328" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G328" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H328" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="I328" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J328" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K328" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="L328" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N328" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="19">
+        <v>45747.440215462964</v>
+      </c>
+      <c r="B329" s="20" t="s">
+        <v>789</v>
+      </c>
+      <c r="C329" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="D329" s="20">
+        <v>2.0222427E7</v>
+      </c>
+      <c r="E329" s="20" t="s">
+        <v>790</v>
+      </c>
+      <c r="F329" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G329" s="21">
+        <v>0.7</v>
+      </c>
+      <c r="H329" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="I329" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J329" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K329" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="L329" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M329" s="20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="15">
+        <v>45747.596171296296</v>
+      </c>
+      <c r="B330" s="16" t="s">
+        <v>791</v>
+      </c>
+      <c r="C330" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="D330" s="16">
+        <v>2.0223821E7</v>
+      </c>
+      <c r="E330" s="16" t="s">
+        <v>792</v>
+      </c>
+      <c r="F330" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G330" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H330" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I330" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J330" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K330" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L330" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="M330" s="16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="19">
+        <v>45747.60223040509</v>
+      </c>
+      <c r="B331" s="20" t="s">
+        <v>793</v>
+      </c>
+      <c r="C331" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="D331" s="20">
+        <v>2.0232205E7</v>
+      </c>
+      <c r="E331" s="20" t="s">
+        <v>794</v>
+      </c>
+      <c r="F331" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G331" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="H331" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I331" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="J331" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="K331" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="L331" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N331" s="22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="15">
+        <v>45747.680911331016</v>
+      </c>
+      <c r="B332" s="16" t="s">
+        <v>795</v>
+      </c>
+      <c r="C332" s="16" t="s">
+        <v>796</v>
+      </c>
+      <c r="D332" s="16">
+        <v>2.0246644E7</v>
+      </c>
+      <c r="E332" s="16" t="s">
+        <v>797</v>
+      </c>
+      <c r="F332" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G332" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H332" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I332" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J332" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K332" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="L332" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N332" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="19">
+        <v>45747.7203075</v>
+      </c>
+      <c r="B333" s="20" t="s">
+        <v>798</v>
+      </c>
+      <c r="C333" s="20" t="s">
+        <v>673</v>
+      </c>
+      <c r="D333" s="20">
+        <v>2.0246428E7</v>
+      </c>
+      <c r="E333" s="20" t="s">
+        <v>799</v>
+      </c>
+      <c r="F333" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="G333" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="H333" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="I333" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J333" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="K333" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="L333" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M333" s="20" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="15">
+        <v>45747.72212103009</v>
+      </c>
+      <c r="B334" s="16" t="s">
+        <v>800</v>
+      </c>
+      <c r="C334" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D334" s="16">
+        <v>2.0202348E7</v>
+      </c>
+      <c r="E334" s="16" t="s">
+        <v>801</v>
+      </c>
+      <c r="F334" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G334" s="17">
+        <v>0.7</v>
+      </c>
+      <c r="H334" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="I334" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="J334" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K334" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="L334" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N334" s="18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="19">
+        <v>45747.72401310185</v>
+      </c>
+      <c r="B335" s="20" t="s">
+        <v>802</v>
+      </c>
+      <c r="C335" s="20" t="s">
+        <v>803</v>
+      </c>
+      <c r="D335" s="20">
+        <v>2.0246413E7</v>
+      </c>
+      <c r="E335" s="20" t="s">
+        <v>804</v>
+      </c>
+      <c r="F335" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G335" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H335" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I335" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J335" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K335" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L335" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M335" s="20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="23">
+        <v>45747.74714744213</v>
+      </c>
+      <c r="B336" s="24" t="s">
+        <v>805</v>
+      </c>
+      <c r="C336" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="D336" s="24">
+        <v>2.024108E7</v>
+      </c>
+      <c r="E336" s="24" t="s">
+        <v>806</v>
+      </c>
+      <c r="F336" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="G336" s="25">
+        <v>0.3</v>
+      </c>
+      <c r="H336" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="I336" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="J336" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="K336" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="L336" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="N336" s="26" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
